--- a/Fellowship Dashboard - June 2026.xlsx
+++ b/Fellowship Dashboard - June 2026.xlsx
@@ -56,7 +56,7 @@
     <author>tc={2D13D56B-EA9B-4AE5-8EC2-CEF13A37B24C}</author>
   </authors>
   <commentList>
-    <comment ref="AE14" authorId="0" xr:uid="{2D13D56B-EA9B-4AE5-8EC2-CEF13A37B24C}">
+    <comment ref="AH14" authorId="0" xr:uid="{2D13D56B-EA9B-4AE5-8EC2-CEF13A37B24C}">
       <text>
         <r>
           <rPr>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t xml:space="preserve">Project summary</t>
   </si>
@@ -227,24 +227,51 @@
     <t>UKL7</t>
   </si>
   <si>
+    <t xml:space="preserve">Estimate F and H as halfway between grades</t>
+  </si>
+  <si>
     <t>UKL8</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>26/27</t>
+  </si>
+  <si>
     <t>UKM3</t>
   </si>
   <si>
+    <t>UKAXF</t>
+  </si>
+  <si>
+    <t>I22</t>
+  </si>
+  <si>
     <t>UKM4</t>
   </si>
   <si>
+    <t>UKAXH</t>
+  </si>
+  <si>
+    <t>I23</t>
+  </si>
+  <si>
     <t>UKM5</t>
   </si>
   <si>
     <t>UKM6</t>
   </si>
   <si>
+    <t xml:space="preserve">Year In Industry</t>
+  </si>
+  <si>
     <t>UKM7</t>
   </si>
   <si>
+    <t xml:space="preserve">Year in Industry = 23,810</t>
+  </si>
+  <si>
     <t>UKMS</t>
   </si>
   <si>
@@ -551,13 +578,22 @@
     <t xml:space="preserve">Rob Hamill</t>
   </si>
   <si>
-    <t>UKAXF</t>
+    <t>Graduates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year in Industry</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t xml:space="preserve">Starts Dec 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Resigns end July 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All external spend is on PhDs - no other external spend</t>
   </si>
   <si>
     <t xml:space="preserve">Project Dashboard- WON 12570-1022 - UKRI</t>
@@ -595,6 +631,99 @@
   </si>
   <si>
     <t xml:space="preserve">Graduates x2 (TBC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year In Industry Students</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiyana Patel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSE (TBC)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FY 26/27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed Errors</t>
+  </si>
+  <si>
+    <t>J25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last year of UKRI FLF is until end of Aug so 5 months, not 3 months - fixing this drastically reduced variance</t>
+  </si>
+  <si>
+    <t>J22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intermediate grades costed lower: UKAXF costed at UKM4 rate, fixed to be halfway between for UKAXF and UKAXH</t>
+  </si>
+  <si>
+    <t>J23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year in industry students not costed for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated based on new information</t>
+  </si>
+  <si>
+    <t>E16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adel -&gt; H after appeal</t>
+  </si>
+  <si>
+    <t>E22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex's resignation date and Rob's starting date accounted for</t>
+  </si>
+  <si>
+    <t>E23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted travel and external spend costs based on FY 25/26 actual expenditure</t>
+  </si>
+  <si>
+    <t>E24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No external spend other than PhDs on UKAEA code</t>
+  </si>
+  <si>
+    <t>E25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promotions for Joel/Wiera corrected based on projected dates</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>27/28</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>28/29</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -607,7 +736,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="12.000000"/>
       <color theme="1"/>
@@ -644,18 +773,11 @@
     </font>
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="11.000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -668,7 +790,6 @@
     <font>
       <b/>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -698,6 +819,13 @@
     </font>
     <font>
       <b/>
+      <sz val="16.000000"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <strike/>
       <sz val="12.000000"/>
       <color theme="1"/>
@@ -707,13 +835,6 @@
     <font>
       <sz val="18.000000"/>
       <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16.000000"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -728,25 +849,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDEDED"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -765,7 +882,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="21">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -775,135 +892,7 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
       </left>
       <right style="medium">
         <color auto="1"/>
@@ -919,7 +908,35 @@
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
@@ -929,26 +946,102 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
       </left>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -1029,217 +1122,10 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
       <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="none"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -1249,7 +1135,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="168">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1264,376 +1150,370 @@
     <xf fontId="6" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="6" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="6" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="7" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="2" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="2" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="6" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="6" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="7" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="2" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="3" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="3" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="4" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="4" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="4" borderId="10" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="5" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="5" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="5" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="5" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="7" fillId="5" borderId="14" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="2" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="6" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="3" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="6" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="2" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="3" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="3" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="4" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="4" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="5" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="5" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="5" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="5" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="6" fillId="5" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="8" fillId="6" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="6" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="6" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="6" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="6" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="6" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="6" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="6" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="7" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="7" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="8" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="8" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="8" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="3" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="3" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="7" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="7" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="17" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="23" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="7" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf fontId="8" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="8" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="8" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="8" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="14" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="9" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf fontId="3" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="9" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="9" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="9" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="10" fillId="0" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf fontId="10" fillId="0" borderId="24" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="9" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="9" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="8" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="8" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="10" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="9" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="29" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="20" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf fontId="11" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="10" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="11" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="10" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="6" borderId="32" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="6" borderId="20" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="6" borderId="6" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="33" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="0" borderId="18" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="34" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="11" fillId="0" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="11" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="6" borderId="29" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="30" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="6" borderId="6" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="17" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="15" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="18" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="16" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="27" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="11" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="17" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="18" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="27" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="12" fillId="0" borderId="37" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="12" fillId="0" borderId="38" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="8" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="8" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="8" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="8" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="7" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="7" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="7" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="14" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="14" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="5" numFmtId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="18" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="6" borderId="2" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="28" numFmtId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="33" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="34" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="17" xfId="0" applyNumberFormat="1"/>
     <xf fontId="15" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="16" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="16" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="11" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1655,8 +1535,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Rockliff, Tasha" id="{B136B8A6-CBBC-BA4D-C3B7-3296E856532D}" userId="S::tasha.rockliff@ukaea.uk::5523177e-4141-40c3-a7e2-0c78d6c92673" providerId="AD"/>
-  <person displayName="Rockliff, Tasha" id="{353716A8-6D7C-C6A3-3CE2-5242C9966DDC}" userId="S::tasha.rockliff@ukaea.uk::5523177e-4141-40c3-a7e2-0c78d6c92673" providerId="Teamlab"/>
+  <person displayName="Rockliff, Tasha" id="{98649FEC-5E65-E418-FA78-FC0F8820C1B2}" userId="S::tasha.rockliff@ukaea.uk::5523177e-4141-40c3-a7e2-0c78d6c92673" providerId="AD"/>
+  <person displayName="Rockliff, Tasha" id="{C9B23960-322D-2C5A-6E53-7914124A4815}" userId="S::tasha.rockliff@ukaea.uk::5523177e-4141-40c3-a7e2-0c78d6c92673" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -2160,7 +2040,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AD14" dT="2025-11-17T15:00:08.08Z" personId="{B136B8A6-CBBC-BA4D-C3B7-3296E856532D}" id="{C468B729-1142-459E-A4F4-DA8E06862930}" done="0">
+  <threadedComment ref="AD14" dT="2025-11-17T15:00:08.08Z" personId="{98649FEC-5E65-E418-FA78-FC0F8820C1B2}" id="{C468B729-1142-459E-A4F4-DA8E06862930}" done="0">
     <text xml:space="preserve">Amend with each update
 </text>
   </threadedComment>
@@ -2169,7 +2049,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AE14" dT="2025-11-17T15:00:08.08Z" personId="{353716A8-6D7C-C6A3-3CE2-5242C9966DDC}" id="{2D13D56B-EA9B-4AE5-8EC2-CEF13A37B24C}" done="0">
+  <threadedComment ref="AH14" dT="2025-11-17T15:00:08.08Z" personId="{C9B23960-322D-2C5A-6E53-7914124A4815}" id="{2D13D56B-EA9B-4AE5-8EC2-CEF13A37B24C}" done="1">
     <text xml:space="preserve">Amend with each update
 </text>
   </threadedComment>
@@ -2178,7 +2058,7 @@
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D7" dT="2026-06-04T10:11:23.86Z" personId="{B136B8A6-CBBC-BA4D-C3B7-3296E856532D}" id="{E619E42B-F8B6-4134-A3D6-5789490C4018}" done="0">
+  <threadedComment ref="D7" dT="2026-06-04T10:11:23.86Z" personId="{98649FEC-5E65-E418-FA78-FC0F8820C1B2}" id="{E619E42B-F8B6-4134-A3D6-5789490C4018}" done="0">
     <text xml:space="preserve">TBC
 </text>
   </threadedComment>
@@ -2187,7 +2067,7 @@
 
 <file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D7" dT="2026-06-04T10:11:23.86Z" personId="{B136B8A6-CBBC-BA4D-C3B7-3296E856532D}" id="{9FB3FA21-711B-4F9D-B9F5-84DD7DA73EF9}" done="0">
+  <threadedComment ref="D7" dT="2026-06-04T10:11:23.86Z" personId="{98649FEC-5E65-E418-FA78-FC0F8820C1B2}" id="{9FB3FA21-711B-4F9D-B9F5-84DD7DA73EF9}" done="0">
     <text xml:space="preserve">TBC
 </text>
   </threadedComment>
@@ -2196,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col bestFit="1" customWidth="1" min="2" max="2" width="24.125"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="11.875"/>
@@ -2464,10 +2344,13 @@
         <f t="shared" si="1"/>
         <v>83.296179200000012</v>
       </c>
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="21">
       <c r="C21" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" s="11">
         <v>104.90000000000001</v>
@@ -2480,14 +2363,39 @@
         <f t="shared" si="1"/>
         <v>113.45984000000001</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="15">
         <f t="shared" si="1"/>
         <v>117.99823360000002</v>
       </c>
+      <c r="H21" s="16"/>
+      <c r="I21" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="22">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
       <c r="C22" s="10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D22" s="11">
         <v>35.289999999999999</v>
@@ -2500,14 +2408,45 @@
         <f t="shared" si="1"/>
         <v>38.169663999999997</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="15">
         <f t="shared" si="1"/>
         <v>39.696450559999995</v>
       </c>
+      <c r="H22" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="16">
+        <f>(D23+D24)/2</f>
+        <v>47.204999999999998</v>
+      </c>
+      <c r="J22" s="19">
+        <f>(E23+E24)/2</f>
+        <v>49.093199999999996</v>
+      </c>
+      <c r="K22" s="19">
+        <f>(F23+F24)/2</f>
+        <v>51.056927999999999</v>
+      </c>
+      <c r="L22" s="19">
+        <f>(G23+G24)/2</f>
+        <v>53.099205120000008</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="23">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
       <c r="C23" s="10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D23" s="11">
         <v>40.399999999999999</v>
@@ -2520,14 +2459,45 @@
         <f t="shared" si="1"/>
         <v>43.696640000000002</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="15">
         <f t="shared" si="1"/>
         <v>45.444505600000006</v>
       </c>
+      <c r="H23" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="16">
+        <f>(D25+D24)/2</f>
+        <v>60.784999999999997</v>
+      </c>
+      <c r="J23" s="19">
+        <f>(E25+E24)/2</f>
+        <v>63.2164</v>
+      </c>
+      <c r="K23" s="19">
+        <f>(F25+F24)/2</f>
+        <v>65.745056000000005</v>
+      </c>
+      <c r="L23" s="19">
+        <f>(G25+G24)/2</f>
+        <v>68.374858240000009</v>
+      </c>
+      <c r="M23" t="s">
+        <v>35</v>
+      </c>
+      <c r="N23" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="24">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
       <c r="C24" s="10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D24" s="11">
         <v>54.009999999999998</v>
@@ -2550,8 +2520,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
       <c r="C25" s="10" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D25" s="11">
         <v>67.560000000000002</v>
@@ -2564,14 +2540,30 @@
         <f t="shared" si="1"/>
         <v>73.072896</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="15">
         <f t="shared" si="1"/>
         <v>75.995811840000002</v>
       </c>
+      <c r="H25" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16">
+        <f>23810/1575</f>
+        <v>15.117460317460317</v>
+      </c>
+      <c r="K25" s="19">
+        <f>J25*1.04</f>
+        <v>15.72215873015873</v>
+      </c>
+      <c r="L25" s="19">
+        <f>K25*1.04</f>
+        <v>16.351045079365079</v>
+      </c>
     </row>
     <row r="26">
       <c r="C26" s="10" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D26" s="11">
         <v>88.780000000000001</v>
@@ -2588,10 +2580,13 @@
         <f t="shared" si="1"/>
         <v>99.865425920000007</v>
       </c>
+      <c r="J26" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="27">
       <c r="C27" s="10" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D27" s="11">
         <v>52.670000000000002</v>
@@ -2611,7 +2606,7 @@
     </row>
     <row r="28">
       <c r="C28" s="10" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D28" s="11">
         <v>46.700000000000003</v>
@@ -2631,7 +2626,7 @@
     </row>
     <row r="29">
       <c r="C29" s="10" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D29" s="11">
         <v>54</v>
@@ -2650,1161 +2645,1161 @@
       </c>
     </row>
     <row r="30" ht="16.5">
-      <c r="C30" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="16">
+      <c r="C30" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="21">
         <v>23.140000000000001</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="22">
         <f t="shared" si="0"/>
         <v>24.0656</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="22">
         <f t="shared" si="1"/>
         <v>25.028224000000002</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="22">
         <f t="shared" si="2"/>
         <v>26.029352960000004</v>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="19">
+      <c r="C31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="24">
         <v>11.5</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="25">
         <f t="shared" si="0"/>
         <v>11.960000000000001</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="25">
         <f t="shared" si="1"/>
         <v>12.438400000000001</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="25">
         <f t="shared" si="2"/>
         <v>12.935936000000002</v>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="19">
+      <c r="C32" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="24">
         <v>14.75</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="25">
         <f t="shared" si="0"/>
         <v>15.34</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="25">
         <f t="shared" si="1"/>
         <v>15.9536</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="25">
         <f t="shared" si="2"/>
         <v>16.591744000000002</v>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="19">
+      <c r="C33" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="24">
         <v>16.5</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="25">
         <f t="shared" si="0"/>
         <v>17.16</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="25">
         <f t="shared" si="1"/>
         <v>17.846399999999999</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="25">
         <f t="shared" si="2"/>
         <v>18.560255999999999</v>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="19">
+      <c r="C34" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="24">
         <v>19.25</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="25">
         <f t="shared" si="0"/>
         <v>20.02</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="25">
         <f t="shared" si="1"/>
         <v>20.820800000000002</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="25">
         <f t="shared" si="2"/>
         <v>21.653632000000002</v>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="19">
+      <c r="C35" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="24">
         <v>21.5</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="25">
         <f t="shared" si="0"/>
         <v>22.359999999999999</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="25">
         <f t="shared" si="1"/>
         <v>23.2544</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="25">
         <f t="shared" si="2"/>
         <v>24.184576</v>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="19">
+      <c r="C36" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="24">
         <v>23.75</v>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="25">
         <f t="shared" si="0"/>
         <v>24.699999999999999</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="25">
         <f t="shared" si="1"/>
         <v>25.687999999999999</v>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="25">
         <f t="shared" si="2"/>
         <v>26.715519999999998</v>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="19">
+      <c r="C37" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="24">
         <v>26.5</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="25">
         <f t="shared" si="0"/>
         <v>27.560000000000002</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="25">
         <f t="shared" si="1"/>
         <v>28.662400000000002</v>
       </c>
-      <c r="G37" s="20">
+      <c r="G37" s="25">
         <f t="shared" si="2"/>
         <v>29.808896000000004</v>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="19">
+      <c r="C38" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="24">
         <v>29</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="25">
         <f t="shared" si="0"/>
         <v>30.16</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="25">
         <f t="shared" si="1"/>
         <v>31.366400000000002</v>
       </c>
-      <c r="G38" s="20">
+      <c r="G38" s="25">
         <f t="shared" si="2"/>
         <v>32.621056000000003</v>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="19">
+      <c r="C39" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="24">
         <v>31.25</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="25">
         <f t="shared" si="0"/>
         <v>32.5</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="25">
         <f t="shared" si="1"/>
         <v>33.800000000000004</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="25">
         <f t="shared" si="2"/>
         <v>35.152000000000008</v>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="19">
+      <c r="C40" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="24">
         <v>33.75</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="25">
         <f t="shared" si="0"/>
         <v>35.100000000000001</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="25">
         <f t="shared" si="1"/>
         <v>36.504000000000005</v>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="25">
         <f t="shared" si="2"/>
         <v>37.964160000000007</v>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41" s="19">
+      <c r="C41" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="24">
         <v>36.5</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="25">
         <f t="shared" si="0"/>
         <v>37.960000000000001</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="25">
         <f t="shared" si="1"/>
         <v>39.478400000000001</v>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="25">
         <f t="shared" si="2"/>
         <v>41.057535999999999</v>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="19">
+      <c r="C42" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="24">
         <v>38.5</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E42" s="25">
         <f t="shared" si="0"/>
         <v>40.039999999999999</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="25">
         <f t="shared" si="1"/>
         <v>41.641600000000004</v>
       </c>
-      <c r="G42" s="20">
+      <c r="G42" s="25">
         <f t="shared" si="2"/>
         <v>43.307264000000004</v>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="19">
+      <c r="C43" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="24">
         <v>41.5</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="25">
         <f t="shared" si="0"/>
         <v>43.160000000000004</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="25">
         <f t="shared" si="1"/>
         <v>44.886400000000002</v>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="25">
         <f t="shared" si="2"/>
         <v>46.681856000000003</v>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="19">
+      <c r="C44" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="24">
         <v>44.25</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="25">
         <f t="shared" si="0"/>
         <v>46.020000000000003</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="25">
         <f t="shared" si="1"/>
         <v>47.860800000000005</v>
       </c>
-      <c r="G44" s="20">
+      <c r="G44" s="25">
         <f t="shared" si="2"/>
         <v>49.77523200000001</v>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45" s="19">
+      <c r="C45" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" s="24">
         <v>48</v>
       </c>
-      <c r="E45" s="20">
+      <c r="E45" s="25">
         <f t="shared" si="0"/>
         <v>49.920000000000002</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="25">
         <f t="shared" si="1"/>
         <v>51.916800000000002</v>
       </c>
-      <c r="G45" s="20">
+      <c r="G45" s="25">
         <f t="shared" si="2"/>
         <v>53.993472000000004</v>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="19">
+      <c r="C46" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="24">
         <v>53.25</v>
       </c>
-      <c r="E46" s="20">
+      <c r="E46" s="25">
         <f t="shared" si="0"/>
         <v>55.380000000000003</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="25">
         <f t="shared" si="1"/>
         <v>57.595200000000006</v>
       </c>
-      <c r="G46" s="20">
+      <c r="G46" s="25">
         <f t="shared" si="2"/>
         <v>59.899008000000009</v>
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" s="19">
+      <c r="C47" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" s="24">
         <v>58.5</v>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="25">
         <f t="shared" si="0"/>
         <v>60.840000000000003</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="25">
         <f t="shared" si="1"/>
         <v>63.273600000000009</v>
       </c>
-      <c r="G47" s="20">
+      <c r="G47" s="25">
         <f t="shared" si="2"/>
         <v>65.804544000000007</v>
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D48" s="19">
+      <c r="C48" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" s="24">
         <v>64.5</v>
       </c>
-      <c r="E48" s="20">
+      <c r="E48" s="25">
         <f t="shared" si="0"/>
         <v>67.079999999999998</v>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="25">
         <f t="shared" si="1"/>
         <v>69.763199999999998</v>
       </c>
-      <c r="G48" s="20">
+      <c r="G48" s="25">
         <f t="shared" si="2"/>
         <v>72.553728000000007</v>
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" s="19">
+      <c r="C49" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D49" s="24">
         <v>70</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="25">
         <f t="shared" si="0"/>
         <v>72.799999999999997</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="25">
         <f t="shared" si="1"/>
         <v>75.712000000000003</v>
       </c>
-      <c r="G49" s="20">
+      <c r="G49" s="25">
         <f t="shared" si="2"/>
         <v>78.740480000000005</v>
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="19">
+      <c r="C50" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" s="24">
         <v>75.849999999999994</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="25">
         <f t="shared" si="0"/>
         <v>78.884</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="25">
         <f t="shared" si="1"/>
         <v>82.039360000000002</v>
       </c>
-      <c r="G50" s="20">
+      <c r="G50" s="25">
         <f t="shared" si="2"/>
         <v>85.320934399999999</v>
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D51" s="19">
+      <c r="C51" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" s="24">
         <v>81.700000000000003</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="25">
         <f t="shared" si="0"/>
         <v>84.968000000000004</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="25">
         <f t="shared" si="1"/>
         <v>88.366720000000001</v>
       </c>
-      <c r="G51" s="20">
+      <c r="G51" s="25">
         <f t="shared" si="2"/>
         <v>91.901388800000007</v>
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D52" s="19">
+      <c r="C52" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="24">
         <v>87.549999999999997</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="25">
         <f t="shared" si="0"/>
         <v>91.052000000000007</v>
       </c>
-      <c r="F52" s="20">
+      <c r="F52" s="25">
         <f t="shared" si="1"/>
         <v>94.694080000000014</v>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="25">
         <f t="shared" si="2"/>
         <v>98.481843200000014</v>
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" s="19">
+      <c r="C53" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="24">
         <v>90</v>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="25">
         <f t="shared" si="0"/>
         <v>93.600000000000009</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="25">
         <f t="shared" si="1"/>
         <v>97.344000000000008</v>
       </c>
-      <c r="G53" s="20">
+      <c r="G53" s="25">
         <f t="shared" si="2"/>
         <v>101.23776000000001</v>
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D54" s="19">
+      <c r="C54" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="24">
         <v>95</v>
       </c>
-      <c r="E54" s="20">
+      <c r="E54" s="25">
         <f t="shared" si="0"/>
         <v>98.799999999999997</v>
       </c>
-      <c r="F54" s="20">
+      <c r="F54" s="25">
         <f t="shared" si="1"/>
         <v>102.752</v>
       </c>
-      <c r="G54" s="20">
+      <c r="G54" s="25">
         <f t="shared" si="2"/>
         <v>106.86207999999999</v>
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="19">
+      <c r="C55" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="24">
         <v>100</v>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="25">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="F55" s="20">
+      <c r="F55" s="25">
         <f t="shared" si="1"/>
         <v>108.16</v>
       </c>
-      <c r="G55" s="20">
+      <c r="G55" s="25">
         <f t="shared" si="2"/>
         <v>112.4864</v>
       </c>
     </row>
     <row r="56">
-      <c r="C56" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" s="19">
+      <c r="C56" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="24">
         <v>105</v>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="25">
         <f t="shared" si="0"/>
         <v>109.2</v>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="25">
         <f t="shared" si="1"/>
         <v>113.56800000000001</v>
       </c>
-      <c r="G56" s="20">
+      <c r="G56" s="25">
         <f t="shared" si="2"/>
         <v>118.11072000000001</v>
       </c>
     </row>
     <row r="57">
-      <c r="C57" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="D57" s="19">
+      <c r="C57" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" s="24">
         <v>110</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="25">
         <f t="shared" si="0"/>
         <v>114.40000000000001</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="25">
         <f t="shared" si="1"/>
         <v>118.97600000000001</v>
       </c>
-      <c r="G57" s="20">
+      <c r="G57" s="25">
         <f t="shared" si="2"/>
         <v>123.73504000000001</v>
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D58" s="19">
+      <c r="C58" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" s="24">
         <v>115</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="25">
         <f t="shared" si="0"/>
         <v>119.60000000000001</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="25">
         <f t="shared" si="1"/>
         <v>124.38400000000001</v>
       </c>
-      <c r="G58" s="20">
+      <c r="G58" s="25">
         <f t="shared" si="2"/>
         <v>129.35936000000001</v>
       </c>
     </row>
     <row r="59">
-      <c r="C59" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D59" s="19">
+      <c r="C59" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="24">
         <v>120</v>
       </c>
-      <c r="E59" s="20">
+      <c r="E59" s="25">
         <f t="shared" si="0"/>
         <v>124.80000000000001</v>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="25">
         <f t="shared" si="1"/>
         <v>129.79200000000003</v>
       </c>
-      <c r="G59" s="20">
+      <c r="G59" s="25">
         <f t="shared" si="2"/>
         <v>134.98368000000005</v>
       </c>
     </row>
     <row r="60" ht="16.5">
-      <c r="C60" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D60" s="22">
+      <c r="C60" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" s="27">
         <v>125</v>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="28">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="F60" s="23">
+      <c r="F60" s="28">
         <f t="shared" si="1"/>
         <v>135.20000000000002</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="28">
         <f t="shared" si="2"/>
         <v>140.60800000000003</v>
       </c>
     </row>
     <row r="61" ht="16.5">
-      <c r="C61" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D61" s="25">
+      <c r="C61" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" s="30">
         <v>56.700000000000003</v>
       </c>
-      <c r="E61" s="26">
+      <c r="E61" s="31">
         <f t="shared" si="0"/>
         <v>58.968000000000004</v>
       </c>
-      <c r="F61" s="26">
+      <c r="F61" s="31">
         <f t="shared" si="1"/>
         <v>61.326720000000009</v>
       </c>
-      <c r="G61" s="26">
+      <c r="G61" s="31">
         <f t="shared" si="2"/>
         <v>63.779788800000013</v>
       </c>
     </row>
     <row r="62">
-      <c r="C62" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D62" s="28">
+      <c r="C62" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="33">
         <v>110</v>
       </c>
-      <c r="E62" s="29">
+      <c r="E62" s="34">
         <f t="shared" si="0"/>
         <v>114.40000000000001</v>
       </c>
-      <c r="F62" s="29">
+      <c r="F62" s="34">
         <f t="shared" si="1"/>
         <v>118.97600000000001</v>
       </c>
-      <c r="G62" s="29">
+      <c r="G62" s="34">
         <f t="shared" si="2"/>
         <v>123.73504000000001</v>
       </c>
     </row>
     <row r="63">
-      <c r="C63" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D63" s="30">
+      <c r="C63" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63" s="35">
         <v>72</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="36">
         <f t="shared" si="0"/>
         <v>74.879999999999995</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="36">
         <f t="shared" si="1"/>
         <v>77.875199999999992</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="36">
         <f t="shared" si="2"/>
         <v>80.990207999999996</v>
       </c>
     </row>
     <row r="64">
-      <c r="C64" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D64" s="30">
+      <c r="C64" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" s="35">
         <v>55</v>
       </c>
-      <c r="E64" s="31">
+      <c r="E64" s="36">
         <f t="shared" si="0"/>
         <v>57.200000000000003</v>
       </c>
-      <c r="F64" s="31">
+      <c r="F64" s="36">
         <f t="shared" si="1"/>
         <v>59.488000000000007</v>
       </c>
-      <c r="G64" s="31">
+      <c r="G64" s="36">
         <f t="shared" si="2"/>
         <v>61.867520000000006</v>
       </c>
     </row>
     <row r="65">
-      <c r="C65" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="D65" s="30">
+      <c r="C65" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="35">
         <v>65</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="36">
         <f t="shared" si="0"/>
         <v>67.600000000000009</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="36">
         <f t="shared" si="1"/>
         <v>70.304000000000016</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="36">
         <f t="shared" si="2"/>
         <v>73.116160000000022</v>
       </c>
     </row>
     <row r="66">
-      <c r="C66" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" s="30">
+      <c r="C66" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="35">
         <v>82</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="36">
         <f t="shared" si="0"/>
         <v>85.280000000000001</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="36">
         <f t="shared" si="1"/>
         <v>88.691200000000009</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="36">
         <f t="shared" si="2"/>
         <v>92.238848000000019</v>
       </c>
     </row>
     <row r="67">
-      <c r="C67" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="D67" s="30">
+      <c r="C67" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" s="35">
         <v>69</v>
       </c>
-      <c r="E67" s="31">
+      <c r="E67" s="36">
         <f t="shared" si="0"/>
         <v>71.760000000000005</v>
       </c>
-      <c r="F67" s="31">
+      <c r="F67" s="36">
         <f t="shared" si="1"/>
         <v>74.630400000000009</v>
       </c>
-      <c r="G67" s="31">
+      <c r="G67" s="36">
         <f t="shared" si="2"/>
         <v>77.615616000000017</v>
       </c>
     </row>
     <row r="68">
-      <c r="C68" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68" s="30">
+      <c r="C68" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68" s="35">
         <v>38</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="36">
         <f t="shared" si="0"/>
         <v>39.520000000000003</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="36">
         <f t="shared" si="1"/>
         <v>41.100800000000007</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="36">
         <f t="shared" si="2"/>
         <v>42.744832000000009</v>
       </c>
     </row>
     <row r="69">
-      <c r="C69" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" s="30">
+      <c r="C69" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D69" s="35">
         <v>60</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="36">
         <f t="shared" si="0"/>
         <v>62.400000000000006</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="36">
         <f t="shared" si="1"/>
         <v>64.896000000000015</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="36">
         <f t="shared" si="2"/>
         <v>67.491840000000025</v>
       </c>
     </row>
     <row r="70">
-      <c r="C70" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D70" s="30">
+      <c r="C70" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70" s="35">
         <v>90</v>
       </c>
-      <c r="E70" s="31">
+      <c r="E70" s="36">
         <f t="shared" si="0"/>
         <v>93.600000000000009</v>
       </c>
-      <c r="F70" s="31">
+      <c r="F70" s="36">
         <f t="shared" si="1"/>
         <v>97.344000000000008</v>
       </c>
-      <c r="G70" s="31">
+      <c r="G70" s="36">
         <f t="shared" si="2"/>
         <v>101.23776000000001</v>
       </c>
     </row>
     <row r="71">
-      <c r="C71" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D71" s="30">
+      <c r="C71" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" s="35">
         <v>120</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="36">
         <f t="shared" si="0"/>
         <v>124.80000000000001</v>
       </c>
-      <c r="F71" s="31">
+      <c r="F71" s="36">
         <f t="shared" si="1"/>
         <v>129.79200000000003</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="36">
         <f t="shared" si="2"/>
         <v>134.98368000000005</v>
       </c>
     </row>
     <row r="72">
-      <c r="C72" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D72" s="30">
+      <c r="C72" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72" s="35">
         <v>100</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="36">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="F72" s="31">
+      <c r="F72" s="36">
         <f t="shared" si="1"/>
         <v>108.16</v>
       </c>
-      <c r="G72" s="31">
+      <c r="G72" s="36">
         <f t="shared" si="2"/>
         <v>112.4864</v>
       </c>
     </row>
     <row r="73">
-      <c r="C73" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D73" s="30">
+      <c r="C73" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D73" s="35">
         <v>50</v>
       </c>
-      <c r="E73" s="31">
+      <c r="E73" s="36">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="F73" s="31">
+      <c r="F73" s="36">
         <f t="shared" si="1"/>
         <v>54.079999999999998</v>
       </c>
-      <c r="G73" s="31">
+      <c r="G73" s="36">
         <f t="shared" si="2"/>
         <v>56.243200000000002</v>
       </c>
     </row>
     <row r="74">
-      <c r="C74" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D74" s="30">
+      <c r="C74" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D74" s="35">
         <v>65</v>
       </c>
-      <c r="E74" s="31">
+      <c r="E74" s="36">
         <f t="shared" si="0"/>
         <v>67.600000000000009</v>
       </c>
-      <c r="F74" s="31">
+      <c r="F74" s="36">
         <f t="shared" si="1"/>
         <v>70.304000000000016</v>
       </c>
-      <c r="G74" s="31">
+      <c r="G74" s="36">
         <f t="shared" si="2"/>
         <v>73.116160000000022</v>
       </c>
     </row>
     <row r="75">
-      <c r="C75" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D75" s="30">
+      <c r="C75" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D75" s="35">
         <v>70</v>
       </c>
-      <c r="E75" s="31">
+      <c r="E75" s="36">
         <f t="shared" si="0"/>
         <v>72.799999999999997</v>
       </c>
-      <c r="F75" s="31">
+      <c r="F75" s="36">
         <f t="shared" si="1"/>
         <v>75.712000000000003</v>
       </c>
-      <c r="G75" s="31">
+      <c r="G75" s="36">
         <f t="shared" si="2"/>
         <v>78.740480000000005</v>
       </c>
     </row>
     <row r="76">
-      <c r="C76" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D76" s="30">
+      <c r="C76" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D76" s="35">
         <v>55</v>
       </c>
-      <c r="E76" s="31">
+      <c r="E76" s="36">
         <f t="shared" ref="E76:E87" si="3">D76*1.04</f>
         <v>57.200000000000003</v>
       </c>
-      <c r="F76" s="31">
+      <c r="F76" s="36">
         <f t="shared" ref="F76:G87" si="4">E76*1.04</f>
         <v>59.488000000000007</v>
       </c>
-      <c r="G76" s="31">
+      <c r="G76" s="36">
         <f t="shared" si="2"/>
         <v>61.867520000000006</v>
       </c>
     </row>
     <row r="77">
-      <c r="C77" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="D77" s="30">
+      <c r="C77" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" s="35">
         <v>105</v>
       </c>
-      <c r="E77" s="31">
+      <c r="E77" s="36">
         <f t="shared" si="3"/>
         <v>109.2</v>
       </c>
-      <c r="F77" s="31">
+      <c r="F77" s="36">
         <f t="shared" si="4"/>
         <v>113.56800000000001</v>
       </c>
-      <c r="G77" s="31">
+      <c r="G77" s="36">
         <f t="shared" si="2"/>
         <v>118.11072000000001</v>
       </c>
     </row>
     <row r="78">
-      <c r="C78" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D78" s="30">
+      <c r="C78" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78" s="35">
         <v>95</v>
       </c>
-      <c r="E78" s="31">
+      <c r="E78" s="36">
         <f t="shared" si="3"/>
         <v>98.799999999999997</v>
       </c>
-      <c r="F78" s="31">
+      <c r="F78" s="36">
         <f t="shared" si="4"/>
         <v>102.752</v>
       </c>
-      <c r="G78" s="31">
+      <c r="G78" s="36">
         <f t="shared" si="2"/>
         <v>106.86207999999999</v>
       </c>
     </row>
     <row r="79">
-      <c r="C79" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D79" s="30">
+      <c r="C79" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D79" s="35">
         <v>46</v>
       </c>
-      <c r="E79" s="31">
+      <c r="E79" s="36">
         <f t="shared" si="3"/>
         <v>47.840000000000003</v>
       </c>
-      <c r="F79" s="31">
+      <c r="F79" s="36">
         <f t="shared" si="4"/>
         <v>49.753600000000006</v>
       </c>
-      <c r="G79" s="31">
+      <c r="G79" s="36">
         <f t="shared" si="2"/>
         <v>51.743744000000007</v>
       </c>
     </row>
     <row r="80">
-      <c r="C80" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="D80" s="30">
+      <c r="C80" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80" s="35">
         <v>115</v>
       </c>
-      <c r="E80" s="31">
+      <c r="E80" s="36">
         <f t="shared" si="3"/>
         <v>119.60000000000001</v>
       </c>
-      <c r="F80" s="31">
+      <c r="F80" s="36">
         <f t="shared" si="4"/>
         <v>124.38400000000001</v>
       </c>
-      <c r="G80" s="31">
+      <c r="G80" s="36">
         <f t="shared" si="2"/>
         <v>129.35936000000001</v>
       </c>
     </row>
     <row r="81">
-      <c r="C81" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D81" s="30">
+      <c r="C81" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D81" s="35">
         <v>170</v>
       </c>
-      <c r="E81" s="31">
+      <c r="E81" s="36">
         <f t="shared" si="3"/>
         <v>176.80000000000001</v>
       </c>
-      <c r="F81" s="31">
+      <c r="F81" s="36">
         <f t="shared" si="4"/>
         <v>183.87200000000001</v>
       </c>
-      <c r="G81" s="31">
+      <c r="G81" s="36">
         <f t="shared" si="2"/>
         <v>191.22688000000002</v>
       </c>
     </row>
     <row r="82">
-      <c r="C82" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D82" s="30">
+      <c r="C82" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D82" s="35">
         <v>135</v>
       </c>
-      <c r="E82" s="31">
+      <c r="E82" s="36">
         <f t="shared" si="3"/>
         <v>140.40000000000001</v>
       </c>
-      <c r="F82" s="31">
+      <c r="F82" s="36">
         <f t="shared" si="4"/>
         <v>146.01600000000002</v>
       </c>
-      <c r="G82" s="31">
+      <c r="G82" s="36">
         <f t="shared" si="2"/>
         <v>151.85664000000003</v>
       </c>
     </row>
     <row r="83">
-      <c r="C83" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" s="30">
+      <c r="C83" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D83" s="35">
         <v>129</v>
       </c>
-      <c r="E83" s="31">
+      <c r="E83" s="36">
         <f t="shared" si="3"/>
         <v>134.16</v>
       </c>
-      <c r="F83" s="31">
+      <c r="F83" s="36">
         <f t="shared" si="4"/>
         <v>139.5264</v>
       </c>
-      <c r="G83" s="31">
+      <c r="G83" s="36">
         <f t="shared" si="2"/>
         <v>145.10745600000001</v>
       </c>
     </row>
     <row r="84">
-      <c r="C84" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D84" s="30">
+      <c r="C84" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D84" s="35">
         <v>87</v>
       </c>
-      <c r="E84" s="31">
+      <c r="E84" s="36">
         <f t="shared" si="3"/>
         <v>90.480000000000004</v>
       </c>
-      <c r="F84" s="31">
+      <c r="F84" s="36">
         <f t="shared" si="4"/>
         <v>94.09920000000001</v>
       </c>
-      <c r="G84" s="31">
+      <c r="G84" s="36">
         <f t="shared" si="2"/>
         <v>97.863168000000016</v>
       </c>
     </row>
     <row r="85">
-      <c r="C85" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D85" s="30">
+      <c r="C85" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85" s="35">
         <v>160</v>
       </c>
-      <c r="E85" s="31">
+      <c r="E85" s="36">
         <f t="shared" si="3"/>
         <v>166.40000000000001</v>
       </c>
-      <c r="F85" s="31">
+      <c r="F85" s="36">
         <f t="shared" si="4"/>
         <v>173.05600000000001</v>
       </c>
-      <c r="G85" s="31">
+      <c r="G85" s="36">
         <f t="shared" si="2"/>
         <v>179.97824000000003</v>
       </c>
     </row>
     <row r="86">
-      <c r="C86" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D86" s="30">
+      <c r="C86" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D86" s="35">
         <v>77</v>
       </c>
-      <c r="E86" s="31">
+      <c r="E86" s="36">
         <f t="shared" si="3"/>
         <v>80.079999999999998</v>
       </c>
-      <c r="F86" s="31">
+      <c r="F86" s="36">
         <f t="shared" si="4"/>
         <v>83.283200000000008</v>
       </c>
-      <c r="G86" s="31">
+      <c r="G86" s="36">
         <f t="shared" si="2"/>
         <v>86.614528000000007</v>
       </c>
     </row>
     <row r="87" ht="16.5">
-      <c r="C87" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D87" s="33">
+      <c r="C87" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="D87" s="38">
         <v>125</v>
       </c>
-      <c r="E87" s="34">
+      <c r="E87" s="39">
         <f t="shared" si="3"/>
         <v>130</v>
       </c>
-      <c r="F87" s="34">
+      <c r="F87" s="39">
         <f t="shared" si="4"/>
         <v>135.20000000000002</v>
       </c>
-      <c r="G87" s="34">
+      <c r="G87" s="39">
         <f t="shared" si="2"/>
         <v>140.60800000000003</v>
       </c>
@@ -3830,8 +3825,8 @@
     <col customWidth="1" min="23" max="23" width="4"/>
     <col customWidth="1" min="24" max="24" width="19"/>
     <col customWidth="1" min="25" max="25" width="16.5"/>
-    <col customWidth="1" min="26" max="27" style="35" width="16.5"/>
-    <col customWidth="1" min="28" max="28" style="36" width="13.875"/>
+    <col customWidth="1" min="26" max="27" style="40" width="16.5"/>
+    <col customWidth="1" min="28" max="28" style="41" width="13.875"/>
     <col customWidth="1" min="29" max="29" width="2.5"/>
     <col customWidth="1" min="30" max="30" width="15.875"/>
     <col customWidth="1" min="31" max="31" width="16.875"/>
@@ -3839,884 +3834,884 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="B1" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
+      <c r="B1" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
     </row>
     <row r="2" ht="16.5" customHeight="1">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="16.5">
-      <c r="B4" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="44"/>
-      <c r="X4" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA4" s="44"/>
-      <c r="AB4" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE4" s="48"/>
+      <c r="B4" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="49"/>
+      <c r="X4" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC4" s="51"/>
+      <c r="AD4" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE4" s="53"/>
     </row>
     <row r="5" ht="120" customHeight="1">
-      <c r="B5" s="49"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="J5" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="M5" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="N5" s="51" t="s">
+      <c r="D5" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="O5" s="52" t="s">
+      <c r="E5" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="P5" s="53" t="s">
+      <c r="F5" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="Q5" s="54" t="s">
+      <c r="H5" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="R5" s="54" t="s">
+      <c r="I5" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="S5" s="54" t="s">
+      <c r="J5" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="T5" s="55" t="s">
+      <c r="K5" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="U5" s="50" t="s">
+      <c r="L5" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="V5" s="56" t="s">
+      <c r="M5" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="X5" s="57" t="s">
+      <c r="N5" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="Y5" s="57" t="s">
+      <c r="O5" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="Z5" s="58" t="s">
+      <c r="P5" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="AA5" s="59" t="s">
+      <c r="Q5" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="AB5" s="60" t="s">
+      <c r="R5" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="AC5" s="46"/>
-      <c r="AD5" s="61"/>
-      <c r="AE5" s="62"/>
+      <c r="S5" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="T5" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="U5" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="V5" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="X5" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y5" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z5" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA5" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB5" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC5" s="51"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="67"/>
     </row>
     <row r="6">
-      <c r="B6" s="63" t="s">
-        <v>124</v>
+      <c r="B6" s="68" t="s">
+        <v>133</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="65" t="s">
+      <c r="D6" s="69" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" s="46"/>
-      <c r="P6" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
-      <c r="X6" s="72"/>
-      <c r="Y6" s="46"/>
-      <c r="Z6" s="73"/>
-      <c r="AA6" s="74"/>
-      <c r="AB6" s="75"/>
-      <c r="AC6" s="46"/>
-      <c r="AD6" s="76"/>
-      <c r="AE6" s="76"/>
+      <c r="K6" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" s="51"/>
+      <c r="P6" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="73"/>
+      <c r="T6" s="74"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="76"/>
+      <c r="X6" s="77"/>
+      <c r="Y6" s="51"/>
+      <c r="Z6" s="78"/>
+      <c r="AA6" s="79"/>
+      <c r="AB6" s="80"/>
+      <c r="AC6" s="51"/>
+      <c r="AD6" s="81"/>
+      <c r="AE6" s="81"/>
     </row>
     <row r="7" ht="16.5">
-      <c r="B7" s="63" t="s">
-        <v>129</v>
+      <c r="B7" s="68" t="s">
+        <v>138</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="77">
+      <c r="D7" s="82">
         <v>0.29999999999999999</v>
       </c>
-      <c r="E7" s="78">
-        <v>0</v>
-      </c>
-      <c r="F7" s="78">
-        <v>0</v>
-      </c>
-      <c r="G7" s="78">
-        <v>0</v>
-      </c>
-      <c r="H7" s="78">
-        <v>0</v>
-      </c>
-      <c r="I7" s="78">
+      <c r="E7" s="83">
+        <v>0</v>
+      </c>
+      <c r="F7" s="83">
+        <v>0</v>
+      </c>
+      <c r="G7" s="83">
+        <v>0</v>
+      </c>
+      <c r="H7" s="83">
+        <v>0</v>
+      </c>
+      <c r="I7" s="83">
         <v>0.90000000000000002</v>
       </c>
-      <c r="J7" s="78">
-        <v>0</v>
-      </c>
-      <c r="K7" s="78">
-        <v>0</v>
-      </c>
-      <c r="L7" s="78">
+      <c r="J7" s="83">
+        <v>0</v>
+      </c>
+      <c r="K7" s="83">
+        <v>0</v>
+      </c>
+      <c r="L7" s="83">
         <v>0.20000000000000001</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="83">
         <v>1</v>
       </c>
-      <c r="N7" s="79">
-        <v>0</v>
-      </c>
-      <c r="O7" s="46"/>
-      <c r="P7" s="80"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="81"/>
-      <c r="T7" s="82"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="84"/>
-      <c r="X7" s="85"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="74"/>
-      <c r="AA7" s="74"/>
-      <c r="AB7" s="75"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="76"/>
-      <c r="AE7" s="76"/>
+      <c r="N7" s="84">
+        <v>0</v>
+      </c>
+      <c r="O7" s="51"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="86"/>
+      <c r="R7" s="86"/>
+      <c r="S7" s="86"/>
+      <c r="T7" s="87"/>
+      <c r="U7" s="88"/>
+      <c r="V7" s="89"/>
+      <c r="X7" s="90"/>
+      <c r="Y7" s="51"/>
+      <c r="Z7" s="79"/>
+      <c r="AA7" s="79"/>
+      <c r="AB7" s="80"/>
+      <c r="AC7" s="51"/>
+      <c r="AD7" s="81"/>
+      <c r="AE7" s="81"/>
     </row>
     <row r="8" ht="16.5">
-      <c r="B8" s="63" t="s">
-        <v>130</v>
+      <c r="B8" s="68" t="s">
+        <v>139</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="86">
+      <c r="D8" s="91">
         <v>24</v>
       </c>
-      <c r="E8" s="87">
-        <v>0</v>
-      </c>
-      <c r="F8" s="87">
-        <v>0</v>
-      </c>
-      <c r="G8" s="87">
-        <v>0</v>
-      </c>
-      <c r="H8" s="87">
-        <v>0</v>
-      </c>
-      <c r="I8" s="87">
+      <c r="E8" s="92">
+        <v>0</v>
+      </c>
+      <c r="F8" s="92">
+        <v>0</v>
+      </c>
+      <c r="G8" s="92">
+        <v>0</v>
+      </c>
+      <c r="H8" s="92">
+        <v>0</v>
+      </c>
+      <c r="I8" s="92">
         <v>948</v>
       </c>
-      <c r="J8" s="87">
-        <v>0</v>
-      </c>
-      <c r="K8" s="87">
-        <v>0</v>
-      </c>
-      <c r="L8" s="87">
-        <v>0</v>
-      </c>
-      <c r="M8" s="87">
+      <c r="J8" s="92">
+        <v>0</v>
+      </c>
+      <c r="K8" s="92">
+        <v>0</v>
+      </c>
+      <c r="L8" s="92">
+        <v>0</v>
+      </c>
+      <c r="M8" s="92">
         <v>809</v>
       </c>
-      <c r="N8" s="88">
-        <v>0</v>
-      </c>
-      <c r="O8" s="89">
+      <c r="N8" s="93">
+        <v>0</v>
+      </c>
+      <c r="O8" s="94">
         <f t="shared" ref="O8:O12" si="5">SUM(D8:N8)</f>
         <v>1781</v>
       </c>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="91"/>
-      <c r="R8" s="91"/>
-      <c r="S8" s="91"/>
-      <c r="T8" s="92">
+      <c r="P8" s="95"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="96"/>
+      <c r="T8" s="97">
         <f t="shared" ref="T8:T9" si="6">SUM(P8:S8)</f>
         <v>0</v>
       </c>
-      <c r="U8" s="91">
+      <c r="U8" s="96">
         <v>627</v>
       </c>
-      <c r="V8" s="93">
+      <c r="V8" s="98">
         <v>215</v>
       </c>
-      <c r="W8" s="94"/>
-      <c r="X8" s="95">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="96">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="74">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="74"/>
-      <c r="AB8" s="97">
+      <c r="W8" s="99"/>
+      <c r="X8" s="100">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="101">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="79">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="79"/>
+      <c r="AB8" s="102">
         <v>95819.570000000007</v>
       </c>
-      <c r="AC8" s="46"/>
-      <c r="AD8" s="98" t="s">
-        <v>131</v>
-      </c>
-      <c r="AE8" s="99"/>
+      <c r="AC8" s="51"/>
+      <c r="AD8" s="103" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE8" s="104"/>
     </row>
     <row r="9" ht="16.5">
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="86">
+      <c r="D9" s="91">
         <v>1091</v>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="92">
         <v>949</v>
       </c>
-      <c r="F9" s="87">
-        <v>0</v>
-      </c>
-      <c r="G9" s="87">
+      <c r="F9" s="92">
+        <v>0</v>
+      </c>
+      <c r="G9" s="92">
         <v>780</v>
       </c>
-      <c r="H9" s="87">
-        <v>0</v>
-      </c>
-      <c r="I9" s="87">
+      <c r="H9" s="92">
+        <v>0</v>
+      </c>
+      <c r="I9" s="92">
         <v>957</v>
       </c>
-      <c r="J9" s="87">
+      <c r="J9" s="92">
         <v>10</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="92">
         <v>58</v>
       </c>
-      <c r="L9" s="87">
+      <c r="L9" s="92">
         <v>358</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="92">
         <v>1393</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="93">
         <v>251</v>
       </c>
-      <c r="O9" s="89">
+      <c r="O9" s="94">
         <f t="shared" si="5"/>
         <v>5847</v>
       </c>
-      <c r="P9" s="90">
+      <c r="P9" s="95">
         <v>7778</v>
       </c>
-      <c r="Q9" s="91">
+      <c r="Q9" s="96">
         <v>8072</v>
       </c>
-      <c r="R9" s="91">
-        <v>0</v>
-      </c>
-      <c r="S9" s="91">
-        <v>0</v>
-      </c>
-      <c r="T9" s="92">
+      <c r="R9" s="96">
+        <v>0</v>
+      </c>
+      <c r="S9" s="96">
+        <v>0</v>
+      </c>
+      <c r="T9" s="97">
         <f t="shared" si="6"/>
         <v>15850</v>
       </c>
-      <c r="U9" s="91">
+      <c r="U9" s="96">
         <v>4370</v>
       </c>
-      <c r="V9" s="93">
+      <c r="V9" s="98">
         <v>27014</v>
       </c>
-      <c r="W9" s="94"/>
-      <c r="X9" s="100">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="91">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="74">
+      <c r="W9" s="99"/>
+      <c r="X9" s="105">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="96">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="79">
         <v>300000</v>
       </c>
-      <c r="AA9" s="74"/>
-      <c r="AB9" s="97">
+      <c r="AA9" s="79"/>
+      <c r="AB9" s="102">
         <v>268870.78999999998</v>
       </c>
-      <c r="AC9" s="46"/>
-      <c r="AD9" s="101"/>
-      <c r="AE9" s="102"/>
+      <c r="AC9" s="51"/>
+      <c r="AD9" s="106"/>
+      <c r="AE9" s="107"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="68" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="103">
+      <c r="D10" s="108">
         <f t="shared" ref="D10:D11" si="7">1575*0.3</f>
         <v>472.5</v>
       </c>
-      <c r="E10" s="104">
-        <v>0</v>
-      </c>
-      <c r="F10" s="104">
-        <v>0</v>
-      </c>
-      <c r="G10" s="104">
-        <v>0</v>
-      </c>
-      <c r="H10" s="104">
-        <v>0</v>
-      </c>
-      <c r="I10" s="89">
+      <c r="E10" s="109">
+        <v>0</v>
+      </c>
+      <c r="F10" s="109">
+        <v>0</v>
+      </c>
+      <c r="G10" s="109">
+        <v>0</v>
+      </c>
+      <c r="H10" s="109">
+        <v>0</v>
+      </c>
+      <c r="I10" s="94">
         <f t="shared" ref="I10:I11" si="8">1575*0.9</f>
         <v>1417.5</v>
       </c>
-      <c r="J10" s="104">
-        <v>0</v>
-      </c>
-      <c r="K10" s="104">
-        <v>0</v>
-      </c>
-      <c r="L10" s="104">
+      <c r="J10" s="109">
+        <v>0</v>
+      </c>
+      <c r="K10" s="109">
+        <v>0</v>
+      </c>
+      <c r="L10" s="109">
         <f t="shared" ref="L10:L11" si="9">1575*0.2</f>
         <v>315</v>
       </c>
-      <c r="M10" s="104">
+      <c r="M10" s="109">
         <f t="shared" ref="M10:M11" si="10">1575</f>
         <v>1575</v>
       </c>
-      <c r="N10" s="105">
-        <v>0</v>
-      </c>
-      <c r="O10" s="89">
+      <c r="N10" s="110">
+        <v>0</v>
+      </c>
+      <c r="O10" s="94">
         <f t="shared" si="5"/>
         <v>3780</v>
       </c>
-      <c r="P10" s="106">
+      <c r="P10" s="111">
         <f>7778+7907</f>
         <v>15685</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="112">
         <f>8072+8306</f>
         <v>16378</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="112">
         <f>15849/2</f>
         <v>7924.5</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="112">
         <f>15849/2</f>
         <v>7924.5</v>
       </c>
-      <c r="T10" s="108">
+      <c r="T10" s="113">
         <f t="shared" ref="T10:T12" si="11">SUM(P10:S10)</f>
         <v>47912</v>
       </c>
-      <c r="U10" s="107">
+      <c r="U10" s="112">
         <v>18000</v>
       </c>
-      <c r="V10" s="109">
+      <c r="V10" s="114">
         <v>47911</v>
       </c>
-      <c r="X10" s="110">
+      <c r="X10" s="115">
         <f>(($D10*Rates!$E$25)+(($E10+$G10+$H10+K10+L10+M10)*Rates!$E$23)+(($F10+H10+J10)*Rates!$E$24)*Rates!$I$11)</f>
         <v>112609.22399999999</v>
       </c>
-      <c r="Y10" s="107">
+      <c r="Y10" s="112">
         <f t="shared" ref="Y10:Y12" si="12">X10+T10+U10+V10</f>
         <v>226432.22399999999</v>
       </c>
-      <c r="Z10" s="74">
+      <c r="Z10" s="79">
         <v>381973.39000000001</v>
       </c>
-      <c r="AA10" s="74">
+      <c r="AA10" s="79">
         <f t="shared" ref="AA10:AA12" si="13">Z10-Y10</f>
         <v>155541.16600000003</v>
       </c>
-      <c r="AB10" s="111">
+      <c r="AB10" s="116">
         <v>30849.549999999999</v>
       </c>
-      <c r="AC10" s="46"/>
-      <c r="AD10" s="112">
+      <c r="AC10" s="51"/>
+      <c r="AD10" s="117">
         <v>1255259.7</v>
       </c>
-      <c r="AE10" s="113"/>
+      <c r="AE10" s="118"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="68" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="103">
+      <c r="D11" s="108">
         <f t="shared" si="7"/>
         <v>472.5</v>
       </c>
-      <c r="E11" s="104">
-        <v>0</v>
-      </c>
-      <c r="F11" s="104">
-        <v>0</v>
-      </c>
-      <c r="G11" s="104">
-        <v>0</v>
-      </c>
-      <c r="H11" s="104">
-        <v>0</v>
-      </c>
-      <c r="I11" s="89">
+      <c r="E11" s="109">
+        <v>0</v>
+      </c>
+      <c r="F11" s="109">
+        <v>0</v>
+      </c>
+      <c r="G11" s="109">
+        <v>0</v>
+      </c>
+      <c r="H11" s="109">
+        <v>0</v>
+      </c>
+      <c r="I11" s="94">
         <f t="shared" si="8"/>
         <v>1417.5</v>
       </c>
-      <c r="J11" s="104">
-        <v>0</v>
-      </c>
-      <c r="K11" s="104">
-        <v>0</v>
-      </c>
-      <c r="L11" s="104">
+      <c r="J11" s="109">
+        <v>0</v>
+      </c>
+      <c r="K11" s="109">
+        <v>0</v>
+      </c>
+      <c r="L11" s="109">
         <f t="shared" si="9"/>
         <v>315</v>
       </c>
-      <c r="M11" s="104">
+      <c r="M11" s="109">
         <f t="shared" si="10"/>
         <v>1575</v>
       </c>
-      <c r="N11" s="105">
-        <v>0</v>
-      </c>
-      <c r="O11" s="89">
+      <c r="N11" s="110">
+        <v>0</v>
+      </c>
+      <c r="O11" s="94">
         <f t="shared" si="5"/>
         <v>3780</v>
       </c>
-      <c r="P11" s="106">
+      <c r="P11" s="111">
         <f>7907+8038.25</f>
         <v>15945.25</v>
       </c>
-      <c r="Q11" s="107">
+      <c r="Q11" s="112">
         <f>8548+8306</f>
         <v>16854</v>
       </c>
-      <c r="R11" s="107">
+      <c r="R11" s="112">
         <f>(15849/2)+(16212/2)</f>
         <v>16030.5</v>
       </c>
-      <c r="S11" s="107">
+      <c r="S11" s="112">
         <f>(15849/2)+(16212/2)</f>
         <v>16030.5</v>
       </c>
-      <c r="T11" s="108">
+      <c r="T11" s="113">
         <f t="shared" si="11"/>
         <v>64860.25</v>
       </c>
-      <c r="U11" s="107">
+      <c r="U11" s="112">
         <v>18000</v>
       </c>
-      <c r="V11" s="109">
+      <c r="V11" s="114">
         <v>64860</v>
       </c>
-      <c r="X11" s="110">
+      <c r="X11" s="115">
         <f>(($D11*Rates!$F$25)+(($E11+$G11+$H11+K11+L11+M11)*Rates!$F$23)+(($F11+H11+J11)*Rates!$F$24)*Rates!$I$11)</f>
         <v>117113.59296000001</v>
       </c>
-      <c r="Y11" s="107">
+      <c r="Y11" s="112">
         <f t="shared" si="12"/>
         <v>264833.84296000004</v>
       </c>
-      <c r="Z11" s="74">
+      <c r="Z11" s="79">
         <v>381973.39000000001</v>
       </c>
-      <c r="AA11" s="74">
+      <c r="AA11" s="79">
         <f t="shared" si="13"/>
         <v>117139.54703999998</v>
       </c>
-      <c r="AB11" s="111"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="114"/>
-      <c r="AE11" s="114"/>
+      <c r="AB11" s="116"/>
+      <c r="AC11" s="51"/>
+      <c r="AD11" s="119"/>
+      <c r="AE11" s="119"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="68" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="103">
+      <c r="D12" s="108">
         <f>(1575*0.3)/2</f>
         <v>236.25</v>
       </c>
-      <c r="E12" s="104">
-        <v>0</v>
-      </c>
-      <c r="F12" s="104">
-        <v>0</v>
-      </c>
-      <c r="G12" s="104">
-        <v>0</v>
-      </c>
-      <c r="H12" s="104">
-        <v>0</v>
-      </c>
-      <c r="I12" s="89">
+      <c r="E12" s="109">
+        <v>0</v>
+      </c>
+      <c r="F12" s="109">
+        <v>0</v>
+      </c>
+      <c r="G12" s="109">
+        <v>0</v>
+      </c>
+      <c r="H12" s="109">
+        <v>0</v>
+      </c>
+      <c r="I12" s="94">
         <f>(1575*0.9)/2</f>
         <v>708.75</v>
       </c>
-      <c r="J12" s="104">
-        <v>0</v>
-      </c>
-      <c r="K12" s="104">
-        <v>0</v>
-      </c>
-      <c r="L12" s="104">
+      <c r="J12" s="109">
+        <v>0</v>
+      </c>
+      <c r="K12" s="109">
+        <v>0</v>
+      </c>
+      <c r="L12" s="109">
         <f>(1575*0.2)/2</f>
         <v>157.5</v>
       </c>
-      <c r="M12" s="104">
+      <c r="M12" s="109">
         <f>1575/2</f>
         <v>787.5</v>
       </c>
-      <c r="N12" s="105">
-        <v>0</v>
-      </c>
-      <c r="O12" s="89">
+      <c r="N12" s="110">
+        <v>0</v>
+      </c>
+      <c r="O12" s="94">
         <f t="shared" si="5"/>
         <v>1890</v>
       </c>
-      <c r="P12" s="106">
+      <c r="P12" s="111">
         <f>(8038+8172.25)/2</f>
         <v>8105.125</v>
       </c>
-      <c r="Q12" s="107">
+      <c r="Q12" s="112">
         <f>(8548+8800)/2</f>
         <v>8674</v>
       </c>
-      <c r="R12" s="107">
+      <c r="R12" s="112">
         <f>(16212+16587)/2</f>
         <v>16399.5</v>
       </c>
-      <c r="S12" s="107">
+      <c r="S12" s="112">
         <f>(16212+16587)/2</f>
         <v>16399.5</v>
       </c>
-      <c r="T12" s="108">
+      <c r="T12" s="113">
         <f t="shared" si="11"/>
         <v>49578.125</v>
       </c>
-      <c r="U12" s="107">
+      <c r="U12" s="112">
         <v>9000</v>
       </c>
-      <c r="V12" s="109">
+      <c r="V12" s="114">
         <v>33106</v>
       </c>
-      <c r="X12" s="110">
+      <c r="X12" s="115">
         <f>(($D12*Rates!$G$25)+(($E12+$G12+$H12+K12+L12+M12)*Rates!$G$23)+(($F12+H12+J12)*Rates!$G$24)*Rates!$I$11)</f>
         <v>60899.068339200006</v>
       </c>
-      <c r="Y12" s="107">
+      <c r="Y12" s="112">
         <f t="shared" si="12"/>
         <v>152583.19333919999</v>
       </c>
-      <c r="Z12" s="74">
+      <c r="Z12" s="79">
         <v>95493.350000000006</v>
       </c>
-      <c r="AA12" s="74">
+      <c r="AA12" s="79">
         <f t="shared" si="13"/>
         <v>-57089.843339199986</v>
       </c>
-      <c r="AB12" s="111"/>
-      <c r="AC12" s="46"/>
-      <c r="AD12" s="115" t="s">
-        <v>132</v>
-      </c>
-      <c r="AE12" s="116"/>
+      <c r="AB12" s="116"/>
+      <c r="AC12" s="51"/>
+      <c r="AD12" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE12" s="104"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="B13" s="63"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="89"/>
-      <c r="K13" s="89"/>
-      <c r="L13" s="89"/>
-      <c r="M13" s="89"/>
-      <c r="N13" s="118"/>
-      <c r="O13" s="89"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="120"/>
-      <c r="R13" s="120"/>
-      <c r="S13" s="120"/>
-      <c r="T13" s="108"/>
-      <c r="U13" s="120"/>
-      <c r="V13" s="121"/>
-      <c r="X13" s="110"/>
-      <c r="Y13" s="107"/>
-      <c r="Z13" s="74"/>
-      <c r="AA13" s="74"/>
-      <c r="AB13" s="111"/>
-      <c r="AC13" s="122"/>
-      <c r="AD13" s="123"/>
-      <c r="AE13" s="124"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="122"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="123"/>
+      <c r="S13" s="123"/>
+      <c r="T13" s="113"/>
+      <c r="U13" s="123"/>
+      <c r="V13" s="124"/>
+      <c r="X13" s="115"/>
+      <c r="Y13" s="112"/>
+      <c r="Z13" s="79"/>
+      <c r="AA13" s="79"/>
+      <c r="AB13" s="116"/>
+      <c r="AC13" s="125"/>
+      <c r="AD13" s="106"/>
+      <c r="AE13" s="126"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="B14" s="125" t="s">
-        <v>133</v>
+      <c r="B14" s="127" t="s">
+        <v>142</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="126">
+      <c r="D14" s="128">
         <f t="shared" ref="D14:T14" si="14">SUM(D8:D13)</f>
         <v>2296.25</v>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="129">
         <f t="shared" si="14"/>
         <v>949</v>
       </c>
-      <c r="F14" s="127">
+      <c r="F14" s="129">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G14" s="127">
+      <c r="G14" s="129">
         <f t="shared" si="14"/>
         <v>780</v>
       </c>
-      <c r="H14" s="127">
+      <c r="H14" s="129">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I14" s="127">
+      <c r="I14" s="129">
         <f t="shared" si="14"/>
         <v>5448.75</v>
       </c>
-      <c r="J14" s="127">
+      <c r="J14" s="129">
         <f t="shared" si="14"/>
         <v>10</v>
       </c>
-      <c r="K14" s="127">
+      <c r="K14" s="129">
         <f t="shared" si="14"/>
         <v>58</v>
       </c>
-      <c r="L14" s="127">
+      <c r="L14" s="129">
         <f t="shared" si="14"/>
         <v>1145.5</v>
       </c>
-      <c r="M14" s="127">
+      <c r="M14" s="129">
         <f t="shared" si="14"/>
         <v>6139.5</v>
       </c>
-      <c r="N14" s="128">
+      <c r="N14" s="130">
         <f t="shared" si="14"/>
         <v>251</v>
       </c>
-      <c r="O14" s="127">
+      <c r="O14" s="129">
         <f t="shared" si="14"/>
         <v>17078</v>
       </c>
-      <c r="P14" s="129">
+      <c r="P14" s="131">
         <f t="shared" si="14"/>
         <v>47513.375</v>
       </c>
-      <c r="Q14" s="130">
+      <c r="Q14" s="132">
         <f t="shared" si="14"/>
         <v>49978</v>
       </c>
-      <c r="R14" s="130">
+      <c r="R14" s="132">
         <f t="shared" si="14"/>
         <v>40354.5</v>
       </c>
-      <c r="S14" s="130">
+      <c r="S14" s="132">
         <f t="shared" si="14"/>
         <v>40354.5</v>
       </c>
-      <c r="T14" s="131">
+      <c r="T14" s="133">
         <f t="shared" si="14"/>
         <v>178200.375</v>
       </c>
-      <c r="U14" s="130">
+      <c r="U14" s="132">
         <f>SUM(U8:U13)</f>
         <v>49997</v>
       </c>
-      <c r="V14" s="131">
+      <c r="V14" s="133">
         <f>SUM(V8:V13)</f>
         <v>173106</v>
       </c>
-      <c r="X14" s="132">
+      <c r="X14" s="134">
         <f>SUM(X8:X12)</f>
         <v>290621.88529920002</v>
       </c>
-      <c r="Y14" s="133">
+      <c r="Y14" s="135">
         <f>SUM(Y8:Y12)</f>
         <v>643849.26029919996</v>
       </c>
-      <c r="Z14" s="134">
+      <c r="Z14" s="136">
         <f>SUM(Z8:Z12)</f>
         <v>1159440.1300000001</v>
       </c>
-      <c r="AA14" s="134"/>
-      <c r="AB14" s="132">
+      <c r="AA14" s="136"/>
+      <c r="AB14" s="134">
         <f>SUM(AB8:AB13)</f>
         <v>395539.90999999997</v>
       </c>
-      <c r="AC14" s="122"/>
-      <c r="AD14" s="135">
+      <c r="AC14" s="125"/>
+      <c r="AD14" s="117">
         <f>(Y10-AB10)+Y11+Y12+AB14</f>
         <v>1008539.6202992001</v>
       </c>
-      <c r="AE14" s="136"/>
+      <c r="AE14" s="118"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="AC15" s="122"/>
+      <c r="AC15" s="125"/>
       <c r="AD15" s="137"/>
       <c r="AE15" s="137"/>
     </row>
@@ -4726,7 +4721,7 @@
       <c r="AE16" s="137"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="AC17" s="122"/>
+      <c r="AC17" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4771,7 +4766,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="greaterThan" id="{1D6B7DE7-A2F8-46EE-B050-B5604EBBCFDF}">
+          <x14:cfRule type="cellIs" priority="2" operator="greaterThan" id="{4402358C-2203-4F7B-91C5-8F551F7B3160}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4788,7 +4783,7 @@
           <xm:sqref>AB8:AB13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="lessThan" id="{75A66920-1952-438A-9575-1D560AE7B68A}">
+          <x14:cfRule type="cellIs" priority="3" operator="lessThan" id="{D307FC7C-14C9-444E-B741-AE276D41C82B}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -4814,959 +4809,1189 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="13.625"/>
+    <col customWidth="1" hidden="1" min="1" max="1" width="0"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="7.63671875"/>
     <col customWidth="1" min="3" max="3" width="4.25"/>
-    <col customWidth="1" min="4" max="16" width="7.625"/>
-    <col customWidth="1" min="17" max="20" width="12.5"/>
-    <col customWidth="1" min="21" max="21" width="18"/>
-    <col customWidth="1" min="22" max="23" width="13.5"/>
-    <col customWidth="1" min="24" max="24" width="4"/>
-    <col customWidth="1" min="25" max="25" width="19"/>
-    <col customWidth="1" min="26" max="26" width="16.5"/>
-    <col customWidth="1" min="27" max="28" style="35" width="16.5"/>
-    <col customWidth="1" min="29" max="29" style="36" width="13.875"/>
-    <col customWidth="1" min="30" max="30" width="2.5"/>
-    <col customWidth="1" min="31" max="31" width="15.875"/>
-    <col customWidth="1" min="32" max="32" width="16.875"/>
-    <col customWidth="1" min="33" max="33" width="3.375"/>
+    <col customWidth="1" min="4" max="19" width="7.625"/>
+    <col customWidth="1" hidden="1" min="20" max="21" width="12.20703125"/>
+    <col customWidth="1" hidden="1" min="22" max="23" width="12.3359375"/>
+    <col customWidth="1" min="24" max="24" width="13.4453125"/>
+    <col bestFit="1" customWidth="1" min="25" max="26" width="13.21484375"/>
+    <col customWidth="1" min="27" max="27" width="4"/>
+    <col customWidth="1" min="28" max="28" width="19"/>
+    <col customWidth="1" min="29" max="29" width="16.5"/>
+    <col customWidth="1" min="30" max="31" style="40" width="16.5"/>
+    <col customWidth="1" min="32" max="32" style="41" width="13.875"/>
+    <col customWidth="1" min="33" max="33" width="2.5"/>
+    <col customWidth="1" min="34" max="34" width="15.875"/>
+    <col customWidth="1" min="35" max="35" width="16.875"/>
+    <col customWidth="1" min="36" max="36" width="3.375"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="B1" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
+      <c r="B1" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="43"/>
     </row>
     <row r="2" ht="16.5" customHeight="1">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="45"/>
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="45"/>
+      <c r="AJ2" s="45"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="16.5">
-      <c r="B4" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="44"/>
-      <c r="Y4" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD4" s="46"/>
-      <c r="AE4" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF4" s="48"/>
+      <c r="B4" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="49"/>
+      <c r="AB4" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG4" s="51"/>
+      <c r="AH4" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="AI4" s="53"/>
     </row>
     <row r="5" ht="120" customHeight="1">
-      <c r="B5" s="49"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="I5" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="J5" s="51" t="s">
+      <c r="D5" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="L5" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="M5" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="N5" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="O5" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="P5" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q5" s="56" t="s">
+        <v>118</v>
+      </c>
+      <c r="R5" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="S5" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="T5" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="U5" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="V5" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="W5" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="X5" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y5" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z5" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB5" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC5" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD5" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE5" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF5" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG5" s="51"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="67"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="69" t="s">
         <v>134</v>
       </c>
-      <c r="K5" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="M5" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="N5" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="O5" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="P5" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q5" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="R5" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="S5" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="T5" s="54" t="s">
-        <v>115</v>
-      </c>
-      <c r="U5" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="V5" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="W5" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y5" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z5" s="57" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA5" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB5" s="59" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC5" s="60" t="s">
-        <v>123</v>
-      </c>
-      <c r="AD5" s="46"/>
-      <c r="AE5" s="61"/>
-      <c r="AF5" s="62"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="63" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="65" t="s">
+      <c r="E6" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="K6" s="65" t="s">
+      <c r="F6" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="70" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="67" t="s">
-        <v>128</v>
-      </c>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="71"/>
-      <c r="Y6" s="72"/>
-      <c r="Z6" s="46"/>
-      <c r="AA6" s="73"/>
-      <c r="AB6" s="74"/>
-      <c r="AC6" s="75"/>
-      <c r="AD6" s="46"/>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
+      <c r="M6" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="N6" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="R6" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="S6" s="51"/>
+      <c r="T6" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="74"/>
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="76"/>
+      <c r="AB6" s="77"/>
+      <c r="AC6" s="51"/>
+      <c r="AD6" s="78"/>
+      <c r="AE6" s="79"/>
+      <c r="AF6" s="80"/>
+      <c r="AG6" s="51"/>
+      <c r="AH6" s="81"/>
+      <c r="AI6" s="81"/>
     </row>
     <row r="7" ht="16.5">
-      <c r="B7" s="63" t="s">
-        <v>129</v>
+      <c r="B7" s="68" t="s">
+        <v>138</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="77">
+      <c r="D7" s="82">
         <v>0.29999999999999999</v>
       </c>
-      <c r="E7" s="78">
-        <v>0</v>
-      </c>
-      <c r="F7" s="78">
-        <v>0</v>
-      </c>
-      <c r="G7" s="78">
-        <v>0</v>
-      </c>
-      <c r="H7" s="78">
-        <v>0</v>
-      </c>
-      <c r="I7" s="78">
+      <c r="E7" s="83">
+        <v>0</v>
+      </c>
+      <c r="F7" s="83">
+        <v>0</v>
+      </c>
+      <c r="G7" s="83">
+        <v>0</v>
+      </c>
+      <c r="H7" s="83">
+        <v>0</v>
+      </c>
+      <c r="I7" s="83">
         <v>0.90000000000000002</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="83">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="K7" s="83">
         <v>1</v>
       </c>
-      <c r="K7" s="78">
-        <v>0</v>
-      </c>
-      <c r="L7" s="78">
-        <v>0</v>
-      </c>
-      <c r="M7" s="78">
+      <c r="L7" s="83">
+        <v>1</v>
+      </c>
+      <c r="M7" s="83">
+        <v>1</v>
+      </c>
+      <c r="N7" s="83">
+        <v>0</v>
+      </c>
+      <c r="O7" s="83">
+        <v>0</v>
+      </c>
+      <c r="P7" s="83">
         <v>0.20000000000000001</v>
       </c>
-      <c r="N7" s="78">
+      <c r="Q7" s="83">
         <v>1</v>
       </c>
-      <c r="O7" s="79">
-        <v>0</v>
-      </c>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="80"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="81"/>
-      <c r="T7" s="81"/>
-      <c r="U7" s="82"/>
-      <c r="V7" s="83"/>
-      <c r="W7" s="84"/>
-      <c r="Y7" s="85"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="74"/>
-      <c r="AB7" s="74"/>
-      <c r="AC7" s="75"/>
-      <c r="AD7" s="46"/>
-      <c r="AE7" s="76"/>
-      <c r="AF7" s="76"/>
+      <c r="R7" s="84">
+        <v>0</v>
+      </c>
+      <c r="S7" s="51"/>
+      <c r="T7" s="85"/>
+      <c r="U7" s="86"/>
+      <c r="V7" s="86"/>
+      <c r="W7" s="86"/>
+      <c r="X7" s="87"/>
+      <c r="Y7" s="88"/>
+      <c r="Z7" s="89"/>
+      <c r="AB7" s="90"/>
+      <c r="AC7" s="51"/>
+      <c r="AD7" s="79"/>
+      <c r="AE7" s="79"/>
+      <c r="AF7" s="80"/>
+      <c r="AG7" s="51"/>
+      <c r="AH7" s="81"/>
+      <c r="AI7" s="81"/>
     </row>
     <row r="8" ht="16.5">
-      <c r="B8" s="63" t="s">
-        <v>130</v>
+      <c r="B8" s="68" t="s">
+        <v>139</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="86">
+      <c r="D8" s="91">
         <v>24</v>
       </c>
-      <c r="E8" s="87">
-        <v>0</v>
-      </c>
-      <c r="F8" s="87">
-        <v>0</v>
-      </c>
-      <c r="G8" s="87">
-        <v>0</v>
-      </c>
-      <c r="H8" s="87">
-        <v>0</v>
-      </c>
-      <c r="I8" s="87">
+      <c r="E8" s="92">
+        <v>0</v>
+      </c>
+      <c r="F8" s="92">
+        <v>0</v>
+      </c>
+      <c r="G8" s="92">
+        <v>0</v>
+      </c>
+      <c r="H8" s="92">
+        <v>0</v>
+      </c>
+      <c r="I8" s="92">
         <v>948</v>
       </c>
-      <c r="J8" s="87">
-        <v>0</v>
-      </c>
-      <c r="K8" s="87">
-        <v>0</v>
-      </c>
-      <c r="L8" s="87">
-        <v>0</v>
-      </c>
-      <c r="M8" s="87">
-        <v>0</v>
-      </c>
-      <c r="N8" s="87">
+      <c r="J8" s="92">
+        <v>0</v>
+      </c>
+      <c r="K8" s="92">
+        <v>0</v>
+      </c>
+      <c r="L8" s="92">
+        <v>0</v>
+      </c>
+      <c r="M8" s="92">
+        <v>0</v>
+      </c>
+      <c r="N8" s="92">
+        <v>0</v>
+      </c>
+      <c r="O8" s="92">
+        <v>0</v>
+      </c>
+      <c r="P8" s="92">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="92">
         <v>809</v>
       </c>
-      <c r="O8" s="88">
-        <v>0</v>
-      </c>
-      <c r="P8" s="89">
-        <f>SUM(D8:O8)</f>
+      <c r="R8" s="93">
+        <v>0</v>
+      </c>
+      <c r="S8" s="94">
+        <f t="shared" ref="S8:S9" si="15">SUM(D8:R8)</f>
         <v>1781</v>
       </c>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="91"/>
-      <c r="S8" s="91"/>
-      <c r="T8" s="91"/>
-      <c r="U8" s="92">
-        <f>SUM(Q8:T8)</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="91">
+      <c r="T8" s="95"/>
+      <c r="U8" s="96"/>
+      <c r="V8" s="96"/>
+      <c r="W8" s="96"/>
+      <c r="X8" s="97">
+        <f t="shared" ref="X8:X9" si="16">SUM(T8:W8)</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="96">
         <v>627</v>
       </c>
-      <c r="W8" s="93">
+      <c r="Z8" s="98">
         <v>215</v>
       </c>
-      <c r="X8" s="94"/>
-      <c r="Y8" s="95">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="96">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="74">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="74"/>
-      <c r="AC8" s="97">
+      <c r="AA8" s="99"/>
+      <c r="AB8" s="100">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="101">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="79">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="79"/>
+      <c r="AF8" s="102">
         <v>95819.570000000007</v>
       </c>
-      <c r="AD8" s="46"/>
-      <c r="AE8" s="98" t="s">
-        <v>131</v>
-      </c>
-      <c r="AF8" s="99"/>
+      <c r="AG8" s="51"/>
+      <c r="AH8" s="103" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI8" s="104"/>
     </row>
     <row r="9" ht="16.5">
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="86">
+      <c r="D9" s="91">
         <v>1091</v>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="92">
         <v>949</v>
       </c>
-      <c r="F9" s="87">
-        <v>0</v>
-      </c>
-      <c r="G9" s="87">
+      <c r="F9" s="92">
+        <v>0</v>
+      </c>
+      <c r="G9" s="92">
         <v>780</v>
       </c>
-      <c r="H9" s="87">
-        <v>0</v>
-      </c>
-      <c r="I9" s="87">
+      <c r="H9" s="92">
+        <v>780</v>
+      </c>
+      <c r="I9" s="92">
         <v>957</v>
       </c>
-      <c r="J9" s="87">
-        <v>0</v>
-      </c>
-      <c r="K9" s="87">
+      <c r="J9" s="92">
+        <v>0</v>
+      </c>
+      <c r="K9" s="92">
+        <v>0</v>
+      </c>
+      <c r="L9" s="92">
+        <v>0</v>
+      </c>
+      <c r="M9" s="92">
+        <v>0</v>
+      </c>
+      <c r="N9" s="92">
         <v>10</v>
       </c>
-      <c r="L9" s="87">
+      <c r="O9" s="92">
         <v>58</v>
       </c>
-      <c r="M9" s="87">
+      <c r="P9" s="92">
         <v>358</v>
       </c>
-      <c r="N9" s="87">
+      <c r="Q9" s="92">
         <v>1393</v>
       </c>
-      <c r="O9" s="88">
+      <c r="R9" s="93">
         <v>251</v>
       </c>
-      <c r="P9" s="89">
-        <f>SUM(D9:O9)</f>
-        <v>5847</v>
-      </c>
-      <c r="Q9" s="90">
+      <c r="S9" s="94">
+        <f t="shared" si="15"/>
+        <v>6627</v>
+      </c>
+      <c r="T9" s="95">
         <v>7778</v>
       </c>
-      <c r="R9" s="91">
+      <c r="U9" s="96">
         <v>8072</v>
       </c>
-      <c r="S9" s="91">
-        <v>0</v>
-      </c>
-      <c r="T9" s="91">
-        <v>0</v>
-      </c>
-      <c r="U9" s="92">
-        <f>SUM(Q9:T9)</f>
+      <c r="V9" s="96">
+        <v>0</v>
+      </c>
+      <c r="W9" s="96">
+        <v>0</v>
+      </c>
+      <c r="X9" s="97">
+        <f t="shared" si="16"/>
         <v>15850</v>
       </c>
-      <c r="V9" s="91">
+      <c r="Y9" s="96">
         <v>4370</v>
       </c>
-      <c r="W9" s="93">
+      <c r="Z9" s="98">
         <v>27014</v>
       </c>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="100">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="91">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="74">
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="105">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="96">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="79">
         <v>300000</v>
       </c>
-      <c r="AB9" s="74"/>
-      <c r="AC9" s="97">
+      <c r="AE9" s="79"/>
+      <c r="AF9" s="102">
         <v>268870.78999999998</v>
       </c>
-      <c r="AD9" s="46"/>
-      <c r="AE9" s="101"/>
-      <c r="AF9" s="102"/>
+      <c r="AG9" s="51"/>
+      <c r="AH9" s="106"/>
+      <c r="AI9" s="107"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="68" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="103">
-        <f t="shared" ref="D10:D11" si="15">1575*0.3</f>
+      <c r="D10" s="108">
+        <f t="shared" ref="D10:D11" si="17">1575*0.3</f>
         <v>472.5</v>
       </c>
-      <c r="E10" s="104">
-        <v>0</v>
-      </c>
-      <c r="F10" s="104">
-        <v>0</v>
-      </c>
-      <c r="G10" s="104">
-        <v>0</v>
-      </c>
-      <c r="H10" s="104">
-        <v>0</v>
-      </c>
-      <c r="I10" s="89">
-        <f t="shared" ref="I10:I11" si="16">1575*0.9</f>
-        <v>1417.5</v>
-      </c>
-      <c r="J10" s="89"/>
-      <c r="K10" s="104">
-        <v>0</v>
-      </c>
-      <c r="L10" s="104">
-        <v>0</v>
-      </c>
-      <c r="M10" s="104">
-        <f t="shared" ref="M10:M11" si="17">1575*0.2</f>
-        <v>315</v>
-      </c>
-      <c r="N10" s="104">
-        <f t="shared" ref="N10:N11" si="18">1575</f>
-        <v>1575</v>
-      </c>
-      <c r="O10" s="105">
-        <v>0</v>
-      </c>
-      <c r="P10" s="89">
-        <f>SUM(D10:O10)</f>
-        <v>3780</v>
-      </c>
-      <c r="Q10" s="106">
+      <c r="E10" s="109">
+        <v>0</v>
+      </c>
+      <c r="F10" s="109">
+        <v>0</v>
+      </c>
+      <c r="G10" s="109">
+        <v>0</v>
+      </c>
+      <c r="H10" s="109">
+        <v>0</v>
+      </c>
+      <c r="I10" s="94">
+        <v>0</v>
+      </c>
+      <c r="J10" s="94">
+        <f>1575*0.6</f>
+        <v>945</v>
+      </c>
+      <c r="K10" s="94">
+        <f>1575*5/12</f>
+        <v>656.25</v>
+      </c>
+      <c r="L10" s="94">
+        <v>0</v>
+      </c>
+      <c r="M10" s="94">
+        <v>0</v>
+      </c>
+      <c r="N10" s="109">
+        <v>0</v>
+      </c>
+      <c r="O10" s="109">
+        <v>0</v>
+      </c>
+      <c r="P10" s="109">
+        <f>1575*0.3</f>
+        <v>472.5</v>
+      </c>
+      <c r="Q10" s="109">
+        <f>1575*4/12*0.8</f>
+        <v>420</v>
+      </c>
+      <c r="R10" s="110">
+        <v>0</v>
+      </c>
+      <c r="S10" s="94">
+        <f t="shared" ref="S10:S12" si="18">SUM(D10:R10)</f>
+        <v>2966.25</v>
+      </c>
+      <c r="T10" s="111">
         <f>7778+7907</f>
         <v>15685</v>
       </c>
-      <c r="R10" s="107">
+      <c r="U10" s="112">
         <f>8072+8306</f>
         <v>16378</v>
       </c>
-      <c r="S10" s="107">
+      <c r="V10" s="112">
         <f>15849/2</f>
         <v>7924.5</v>
       </c>
-      <c r="T10" s="107">
+      <c r="W10" s="112">
         <f>15849/2</f>
         <v>7924.5</v>
       </c>
-      <c r="U10" s="108">
-        <f>SUM(Q10:T10)</f>
+      <c r="X10" s="113">
+        <f t="shared" ref="X10:X12" si="19">SUM(T10:W10)</f>
         <v>47912</v>
       </c>
-      <c r="V10" s="107">
-        <v>18000</v>
-      </c>
-      <c r="W10" s="109">
-        <v>47911</v>
-      </c>
-      <c r="Y10" s="110">
-        <f>(($D10*Rates!$E$25)+(($E10+$G10+$H10+L10+M10+N10)*Rates!$E$23)+(($F10+H10+K10)*Rates!$E$24)*Rates!$I$11)</f>
-        <v>112609.22399999999</v>
-      </c>
-      <c r="Z10" s="107">
-        <f>Y10+U10+V10+W10</f>
-        <v>226432.22399999999</v>
-      </c>
-      <c r="AA10" s="74">
+      <c r="Y10" s="112">
+        <v>15000</v>
+      </c>
+      <c r="Z10" s="114">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="115">
+        <f>((($D10*Rates!$E$25)+($E10*Rates!$E$23)+($F10*Rates!$E$24)+($G10*Rates!$E$23)+($H10*Rates!$J$22)+($I10*Rates!$E$24)+($J10*Rates!$J$23)+($K10*Rates!$J$22)+($L10*Rates!$E$16)+($P10*Rates!$E$23)+($Q10*Rates!$E$23))*Rates!$I$11)</f>
+        <v>227717.24429999999</v>
+      </c>
+      <c r="AC10" s="112">
+        <f t="shared" ref="AC10:AC12" si="20">AB10+X10+Y10+Z10</f>
+        <v>290629.24430000002</v>
+      </c>
+      <c r="AD10" s="79">
         <v>381973.39000000001</v>
       </c>
-      <c r="AB10" s="74">
-        <f>AA10-Z10</f>
-        <v>155541.16600000003</v>
-      </c>
-      <c r="AC10" s="111">
+      <c r="AE10" s="79">
+        <f t="shared" ref="AE10:AE12" si="21">AD10-AC10</f>
+        <v>91344.145699999994</v>
+      </c>
+      <c r="AF10" s="116">
         <v>30849.549999999999</v>
       </c>
-      <c r="AD10" s="46"/>
-      <c r="AE10" s="112">
+      <c r="AG10" s="51"/>
+      <c r="AH10" s="117">
         <v>1255259.7</v>
       </c>
-      <c r="AF10" s="113"/>
+      <c r="AI10" s="118"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="68" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="103">
-        <f t="shared" si="15"/>
+      <c r="D11" s="108">
+        <f t="shared" si="17"/>
         <v>472.5</v>
       </c>
-      <c r="E11" s="104">
-        <v>0</v>
-      </c>
-      <c r="F11" s="104">
-        <v>0</v>
-      </c>
-      <c r="G11" s="104">
-        <v>0</v>
-      </c>
-      <c r="H11" s="104">
-        <v>0</v>
-      </c>
-      <c r="I11" s="89">
-        <f t="shared" si="16"/>
+      <c r="E11" s="109">
+        <v>0</v>
+      </c>
+      <c r="F11" s="109">
+        <v>0</v>
+      </c>
+      <c r="G11" s="109">
+        <v>0</v>
+      </c>
+      <c r="H11" s="109">
+        <v>0</v>
+      </c>
+      <c r="I11" s="94">
+        <v>0</v>
+      </c>
+      <c r="J11" s="94">
+        <f>1575*0.9</f>
         <v>1417.5</v>
       </c>
-      <c r="J11" s="89"/>
-      <c r="K11" s="104">
-        <v>0</v>
-      </c>
-      <c r="L11" s="104">
-        <v>0</v>
-      </c>
-      <c r="M11" s="104">
-        <f t="shared" si="17"/>
-        <v>315</v>
-      </c>
-      <c r="N11" s="104">
+      <c r="K11" s="94">
+        <v>1575</v>
+      </c>
+      <c r="L11" s="94">
+        <v>0</v>
+      </c>
+      <c r="M11" s="94">
+        <v>0</v>
+      </c>
+      <c r="N11" s="109">
+        <v>0</v>
+      </c>
+      <c r="O11" s="109">
+        <v>0</v>
+      </c>
+      <c r="P11" s="109">
+        <f>0.1*1575</f>
+        <v>157.5</v>
+      </c>
+      <c r="Q11" s="109">
+        <v>0</v>
+      </c>
+      <c r="R11" s="110">
+        <v>0</v>
+      </c>
+      <c r="S11" s="94">
         <f t="shared" si="18"/>
-        <v>1575</v>
-      </c>
-      <c r="O11" s="105">
-        <v>0</v>
-      </c>
-      <c r="P11" s="89">
-        <f>SUM(D11:O11)</f>
-        <v>3780</v>
-      </c>
-      <c r="Q11" s="106">
+        <v>3622.5</v>
+      </c>
+      <c r="T11" s="111">
         <f>7907+8038.25</f>
         <v>15945.25</v>
       </c>
-      <c r="R11" s="107">
+      <c r="U11" s="112">
         <f>8548+8306</f>
         <v>16854</v>
       </c>
-      <c r="S11" s="107">
+      <c r="V11" s="112">
         <f>(15849/2)+(16212/2)</f>
         <v>16030.5</v>
       </c>
-      <c r="T11" s="107">
+      <c r="W11" s="112">
         <f>(15849/2)+(16212/2)</f>
         <v>16030.5</v>
       </c>
-      <c r="U11" s="108">
-        <f>SUM(Q11:T11)</f>
+      <c r="X11" s="113">
+        <f t="shared" si="19"/>
         <v>64860.25</v>
       </c>
-      <c r="V11" s="107">
-        <v>18000</v>
-      </c>
-      <c r="W11" s="109">
-        <v>64860</v>
-      </c>
-      <c r="Y11" s="110">
-        <f>(($D11*Rates!$F$25)+(($E11+$G11+$H11+L11+M11+N11)*Rates!$F$23)+(($F11+H11+K11)*Rates!$F$24)*Rates!$I$11)</f>
-        <v>117113.59296000001</v>
-      </c>
-      <c r="Z11" s="107">
-        <f>Y11+U11+V11+W11</f>
-        <v>264833.84296000004</v>
-      </c>
-      <c r="AA11" s="74">
+      <c r="Y11" s="112">
+        <v>15000</v>
+      </c>
+      <c r="Z11" s="114">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="115">
+        <f>((($D11*Rates!$F$25)+($E11*Rates!$F$23)+($F11*Rates!$F$24)+($G11*Rates!$F$23)+($H11*Rates!$K$22)+($I11*Rates!$F$24)+($J11*Rates!$K$23)+($K11*Rates!$K$22)+($L11*Rates!$F$16)+($P11*Rates!$F$23)+($Q11*Rates!$F$23))*Rates!$I$11)</f>
+        <v>301024.419696</v>
+      </c>
+      <c r="AC11" s="112">
+        <f t="shared" si="20"/>
+        <v>380884.669696</v>
+      </c>
+      <c r="AD11" s="79">
         <v>381973.39000000001</v>
       </c>
-      <c r="AB11" s="74">
-        <f>AA11-Z11</f>
-        <v>117139.54703999998</v>
-      </c>
-      <c r="AC11" s="111"/>
-      <c r="AD11" s="46"/>
-      <c r="AE11" s="114"/>
-      <c r="AF11" s="114"/>
+      <c r="AE11" s="79">
+        <f t="shared" si="21"/>
+        <v>1088.7203040000168</v>
+      </c>
+      <c r="AF11" s="116"/>
+      <c r="AG11" s="51"/>
+      <c r="AH11" s="119"/>
+      <c r="AI11" s="119"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="68" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="103">
-        <f>(1575*0.3)/2</f>
-        <v>236.25</v>
-      </c>
-      <c r="E12" s="104">
-        <v>0</v>
-      </c>
-      <c r="F12" s="104">
-        <v>0</v>
-      </c>
-      <c r="G12" s="104">
-        <v>0</v>
-      </c>
-      <c r="H12" s="104">
-        <v>0</v>
-      </c>
-      <c r="I12" s="89">
-        <f>(1575*0.9)/2</f>
-        <v>708.75</v>
-      </c>
-      <c r="J12" s="89"/>
-      <c r="K12" s="104">
-        <v>0</v>
-      </c>
-      <c r="L12" s="104">
-        <v>0</v>
-      </c>
-      <c r="M12" s="104">
-        <f>(1575*0.2)/2</f>
-        <v>157.5</v>
-      </c>
-      <c r="N12" s="104">
-        <f>1575/2</f>
-        <v>787.5</v>
-      </c>
-      <c r="O12" s="105">
-        <v>0</v>
-      </c>
-      <c r="P12" s="89">
-        <f>SUM(D12:O12)</f>
-        <v>1890</v>
-      </c>
-      <c r="Q12" s="106">
+      <c r="D12" s="108">
+        <f>1575*5/12*0.3</f>
+        <v>196.875</v>
+      </c>
+      <c r="E12" s="109">
+        <v>0</v>
+      </c>
+      <c r="F12" s="109">
+        <v>0</v>
+      </c>
+      <c r="G12" s="109">
+        <v>0</v>
+      </c>
+      <c r="H12" s="109">
+        <v>0</v>
+      </c>
+      <c r="I12" s="94">
+        <v>0</v>
+      </c>
+      <c r="J12" s="94">
+        <f>1575*5/12*0.9</f>
+        <v>590.625</v>
+      </c>
+      <c r="K12" s="94">
+        <f>1575*5/12</f>
+        <v>656.25</v>
+      </c>
+      <c r="L12" s="94">
+        <v>0</v>
+      </c>
+      <c r="M12" s="94">
+        <v>0</v>
+      </c>
+      <c r="N12" s="109">
+        <v>0</v>
+      </c>
+      <c r="O12" s="109">
+        <v>0</v>
+      </c>
+      <c r="P12" s="109">
+        <f>1575*5/12*0.1</f>
+        <v>65.625</v>
+      </c>
+      <c r="Q12" s="109">
+        <v>0</v>
+      </c>
+      <c r="R12" s="110">
+        <v>0</v>
+      </c>
+      <c r="S12" s="94">
+        <f t="shared" si="18"/>
+        <v>1509.375</v>
+      </c>
+      <c r="T12" s="111">
         <f>(8038+8172.25)/2</f>
         <v>8105.125</v>
       </c>
-      <c r="R12" s="107">
+      <c r="U12" s="112">
         <f>(8548+8800)/2</f>
         <v>8674</v>
       </c>
-      <c r="S12" s="107">
+      <c r="V12" s="112">
         <f>(16212+16587)/2</f>
         <v>16399.5</v>
       </c>
-      <c r="T12" s="107">
+      <c r="W12" s="112">
         <f>(16212+16587)/2</f>
         <v>16399.5</v>
       </c>
-      <c r="U12" s="108">
-        <f>SUM(Q12:T12)</f>
+      <c r="X12" s="113">
+        <f t="shared" si="19"/>
         <v>49578.125</v>
       </c>
-      <c r="V12" s="107">
-        <v>9000</v>
-      </c>
-      <c r="W12" s="109">
-        <v>33106</v>
-      </c>
-      <c r="Y12" s="110">
-        <f>(($D12*Rates!$G$25)+(($E12+$G12+$H12+L12+M12+N12)*Rates!$G$23)+(($F12+H12+K12)*Rates!$G$24)*Rates!$I$11)</f>
-        <v>60899.068339200006</v>
-      </c>
-      <c r="Z12" s="107">
-        <f>Y12+U12+V12+W12</f>
-        <v>152583.19333919999</v>
-      </c>
-      <c r="AA12" s="74">
+      <c r="Y12" s="112">
+        <v>7500</v>
+      </c>
+      <c r="Z12" s="114">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="115">
+        <f>((($D12*Rates!$G$25)+($E12*Rates!$G$23)+($F12*Rates!$G$24)+($G12*Rates!$G$23)+($H12*Rates!$L$22)+($I12*Rates!$G$24)+($J12*Rates!$L$23)+($K12*Rates!$L$22)+($L12*Rates!$G$16)+($P12*Rates!$G$23)+($Q12*Rates!$G$23))*Rates!$I$11)</f>
+        <v>130443.9152016</v>
+      </c>
+      <c r="AC12" s="112">
+        <f t="shared" si="20"/>
+        <v>187522.0402016</v>
+      </c>
+      <c r="AD12" s="79">
         <v>95493.350000000006</v>
       </c>
-      <c r="AB12" s="74">
-        <f>AA12-Z12</f>
-        <v>-57089.843339199986</v>
-      </c>
-      <c r="AC12" s="111"/>
-      <c r="AD12" s="46"/>
-      <c r="AE12" s="115" t="s">
-        <v>132</v>
+      <c r="AE12" s="79">
+        <f t="shared" si="21"/>
+        <v>-92028.690201599995</v>
       </c>
       <c r="AF12" s="116"/>
+      <c r="AG12" s="51"/>
+      <c r="AH12" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI12" s="104"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="B13" s="63"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="89"/>
-      <c r="K13" s="89"/>
-      <c r="L13" s="89"/>
-      <c r="M13" s="89"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="118"/>
-      <c r="P13" s="89"/>
-      <c r="Q13" s="119"/>
-      <c r="R13" s="120"/>
-      <c r="S13" s="120"/>
-      <c r="T13" s="120"/>
-      <c r="U13" s="108"/>
-      <c r="V13" s="120"/>
-      <c r="W13" s="121"/>
-      <c r="Y13" s="110"/>
-      <c r="Z13" s="107"/>
-      <c r="AA13" s="74"/>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="111"/>
-      <c r="AD13" s="122"/>
-      <c r="AE13" s="123"/>
-      <c r="AF13" s="124"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="94"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="121"/>
+      <c r="S13" s="94"/>
+      <c r="T13" s="122"/>
+      <c r="U13" s="123"/>
+      <c r="V13" s="123"/>
+      <c r="W13" s="123"/>
+      <c r="X13" s="113"/>
+      <c r="Y13" s="123"/>
+      <c r="Z13" s="124"/>
+      <c r="AB13" s="115"/>
+      <c r="AC13" s="112"/>
+      <c r="AD13" s="79"/>
+      <c r="AE13" s="79"/>
+      <c r="AF13" s="116"/>
+      <c r="AG13" s="125"/>
+      <c r="AH13" s="106"/>
+      <c r="AI13" s="126"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="B14" s="125" t="s">
-        <v>133</v>
+      <c r="B14" s="127" t="s">
+        <v>142</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="126">
-        <f t="shared" ref="D14:P14" si="19">SUM(D8:D13)</f>
-        <v>2296.25</v>
-      </c>
-      <c r="E14" s="127">
-        <f t="shared" si="19"/>
+      <c r="D14" s="128">
+        <f t="shared" ref="D14:S14" si="22">SUM(D8:D13)</f>
+        <v>2256.875</v>
+      </c>
+      <c r="E14" s="129">
+        <f t="shared" si="22"/>
         <v>949</v>
       </c>
-      <c r="F14" s="127">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="127">
-        <f t="shared" si="19"/>
+      <c r="F14" s="129">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="129">
+        <f>SUM(G8:G13)</f>
         <v>780</v>
       </c>
-      <c r="H14" s="127">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="127">
-        <f t="shared" si="19"/>
-        <v>5448.75</v>
-      </c>
-      <c r="J14" s="127"/>
-      <c r="K14" s="127">
-        <f t="shared" si="19"/>
+      <c r="H14" s="129">
+        <f t="shared" si="22"/>
+        <v>780</v>
+      </c>
+      <c r="I14" s="129">
+        <f t="shared" si="22"/>
+        <v>1905</v>
+      </c>
+      <c r="J14" s="129">
+        <f>SUM(J8:J13)</f>
+        <v>2953.125</v>
+      </c>
+      <c r="K14" s="129">
+        <f>SUM(K8:K13)</f>
+        <v>2887.5</v>
+      </c>
+      <c r="L14" s="129">
+        <f>SUM(L8:L13)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="129">
+        <f>SUM(M8:M13)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="129">
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="L14" s="127">
-        <f t="shared" si="19"/>
+      <c r="O14" s="129">
+        <f t="shared" si="22"/>
         <v>58</v>
       </c>
-      <c r="M14" s="127">
-        <f t="shared" si="19"/>
-        <v>1145.5</v>
-      </c>
-      <c r="N14" s="127">
-        <f t="shared" si="19"/>
-        <v>6139.5</v>
-      </c>
-      <c r="O14" s="128">
-        <f t="shared" si="19"/>
+      <c r="P14" s="129">
+        <f t="shared" si="22"/>
+        <v>1053.625</v>
+      </c>
+      <c r="Q14" s="129">
+        <f t="shared" si="22"/>
+        <v>2622</v>
+      </c>
+      <c r="R14" s="130">
+        <f t="shared" si="22"/>
         <v>251</v>
       </c>
-      <c r="P14" s="127">
-        <f t="shared" si="19"/>
-        <v>17078</v>
-      </c>
-      <c r="Q14" s="129">
-        <f t="shared" ref="Q14:U14" si="20">SUM(Q8:Q13)</f>
+      <c r="S14" s="129">
+        <f t="shared" si="22"/>
+        <v>16506.125</v>
+      </c>
+      <c r="T14" s="131">
+        <f t="shared" ref="T14:X14" si="23">SUM(T8:T13)</f>
         <v>47513.375</v>
       </c>
-      <c r="R14" s="130">
-        <f t="shared" si="20"/>
+      <c r="U14" s="132">
+        <f t="shared" si="23"/>
         <v>49978</v>
       </c>
-      <c r="S14" s="130">
-        <f t="shared" si="20"/>
+      <c r="V14" s="132">
+        <f t="shared" si="23"/>
         <v>40354.5</v>
       </c>
-      <c r="T14" s="130">
-        <f t="shared" si="20"/>
+      <c r="W14" s="132">
+        <f t="shared" si="23"/>
         <v>40354.5</v>
       </c>
-      <c r="U14" s="131">
-        <f t="shared" si="20"/>
+      <c r="X14" s="133">
+        <f t="shared" si="23"/>
         <v>178200.375</v>
       </c>
-      <c r="V14" s="130">
-        <f>SUM(V8:V13)</f>
-        <v>49997</v>
-      </c>
-      <c r="W14" s="131">
-        <f>SUM(W8:W13)</f>
-        <v>173106</v>
-      </c>
       <c r="Y14" s="132">
-        <f>SUM(Y8:Y12)</f>
-        <v>290621.88529920002</v>
+        <f>SUM(Y8:Y13)</f>
+        <v>42497</v>
       </c>
       <c r="Z14" s="133">
-        <f>SUM(Z8:Z12)</f>
-        <v>643849.26029919996</v>
-      </c>
-      <c r="AA14" s="134">
-        <f>SUM(AA8:AA12)</f>
+        <f>SUM(Z8:Z13)</f>
+        <v>27229</v>
+      </c>
+      <c r="AB14" s="134">
+        <f>SUM(AB8:AB12)</f>
+        <v>659185.57919760002</v>
+      </c>
+      <c r="AC14" s="135">
+        <f>SUM(AC8:AC12)</f>
+        <v>859035.95419760002</v>
+      </c>
+      <c r="AD14" s="136">
+        <f>SUM(AD8:AD12)</f>
         <v>1159440.1300000001</v>
       </c>
-      <c r="AB14" s="134"/>
-      <c r="AC14" s="132">
-        <f>SUM(AC8:AC13)</f>
+      <c r="AE14" s="136"/>
+      <c r="AF14" s="134">
+        <f>SUM(AF8:AF13)</f>
         <v>395539.90999999997</v>
       </c>
-      <c r="AD14" s="122"/>
-      <c r="AE14" s="135">
-        <f>(Z10-AC10)+Z11+Z12+AC14</f>
-        <v>1008539.6202992001</v>
-      </c>
-      <c r="AF14" s="136"/>
+      <c r="AG14" s="125"/>
+      <c r="AH14" s="117">
+        <f>(AC10-AF10)+AC11+AC12+AF14</f>
+        <v>1223726.3141975999</v>
+      </c>
+      <c r="AI14" s="118"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="J15" t="s">
-        <v>136</v>
-      </c>
-      <c r="N15" t="s">
-        <v>137</v>
-      </c>
-      <c r="AD15" s="122"/>
-      <c r="AE15" s="137"/>
-      <c r="AF15" s="137"/>
+      <c r="K15" t="s">
+        <v>147</v>
+      </c>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="Q15" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG15" s="125"/>
+      <c r="AH15" s="137"/>
+      <c r="AI15" s="137"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="Z16" s="138"/>
-      <c r="AE16" s="137"/>
-      <c r="AF16" s="137"/>
+      <c r="AC16" s="138"/>
+      <c r="AH16" s="137"/>
+      <c r="AI16" s="137"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="AD17" s="122"/>
+      <c r="J17" s="140"/>
+      <c r="K17" s="141"/>
+      <c r="L17" s="141"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="142"/>
+      <c r="AB17" s="140"/>
+      <c r="AC17" s="140"/>
+      <c r="AD17" s="140"/>
+      <c r="AE17" s="141"/>
+      <c r="AF17" s="143"/>
+      <c r="AG17" s="125"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="J18" s="140"/>
+      <c r="K18" s="140"/>
+      <c r="L18" s="140"/>
+      <c r="M18" s="140"/>
+      <c r="N18" s="140"/>
+      <c r="AB18" s="140"/>
+      <c r="AC18" s="140"/>
+      <c r="AD18" s="140"/>
+      <c r="AE18" s="140"/>
+      <c r="AF18" s="144"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="J19" s="140"/>
+      <c r="K19" s="140"/>
+      <c r="L19" s="140"/>
+      <c r="M19" s="140"/>
+      <c r="N19" s="140"/>
+      <c r="AB19" s="140"/>
+      <c r="AC19" s="140"/>
+      <c r="AD19" s="140"/>
+      <c r="AE19" s="140"/>
+      <c r="AF19" s="144"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="J20" s="145"/>
+      <c r="K20" s="140"/>
+      <c r="L20" s="140"/>
+      <c r="M20" s="140"/>
+      <c r="N20" s="140"/>
+      <c r="AB20" s="140"/>
+      <c r="AC20" s="140"/>
+      <c r="AD20" s="140"/>
+      <c r="AE20" s="140"/>
+      <c r="AF20" s="144"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="J21" s="145"/>
+      <c r="K21" s="138"/>
+      <c r="L21" s="138"/>
+      <c r="M21" s="138"/>
+      <c r="N21" s="138"/>
+      <c r="AB21" s="140"/>
+      <c r="AC21" s="140"/>
+      <c r="AD21" s="140"/>
+      <c r="AE21" s="140"/>
+      <c r="AF21" s="144"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="J22" s="140"/>
+      <c r="K22" s="146"/>
+      <c r="L22" s="146"/>
+      <c r="M22" s="146"/>
+      <c r="N22" s="146"/>
+      <c r="AB22" s="140"/>
+      <c r="AC22" s="140"/>
+      <c r="AD22" s="140"/>
+      <c r="AE22" s="147"/>
+      <c r="AF22" s="144"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="J23" s="140"/>
+      <c r="K23" s="148"/>
+      <c r="L23" s="148"/>
+      <c r="M23" s="148"/>
+      <c r="N23" s="148"/>
+      <c r="AB23" s="140"/>
+      <c r="AC23" s="140"/>
+      <c r="AD23" s="140"/>
+      <c r="AE23" s="147"/>
+      <c r="AF23" s="144"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="J24" s="140"/>
+      <c r="K24" s="142"/>
+      <c r="L24" s="142"/>
+      <c r="M24" s="142"/>
+      <c r="N24" s="142"/>
+      <c r="AB24" s="140"/>
+      <c r="AC24" s="140"/>
+      <c r="AD24" s="140"/>
+      <c r="AE24" s="140"/>
+      <c r="AF24" s="144"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="J25" s="140"/>
+      <c r="K25" s="142"/>
+      <c r="L25" s="142"/>
+      <c r="M25" s="142"/>
+      <c r="N25" s="142"/>
+      <c r="AB25" s="140"/>
+      <c r="AC25" s="140"/>
+      <c r="AD25" s="140"/>
+      <c r="AE25" s="140"/>
+      <c r="AF25" s="144"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="J26" s="140"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="142"/>
+      <c r="N26" s="142"/>
+      <c r="AB26" s="140"/>
+      <c r="AC26" s="140"/>
+      <c r="AD26" s="140"/>
+      <c r="AE26" s="140"/>
+      <c r="AF26" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B1:AG2"/>
+    <mergeCell ref="B1:AJ2"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AE4:AF5"/>
-    <mergeCell ref="Q6:U6"/>
-    <mergeCell ref="AE8:AF8"/>
-    <mergeCell ref="AE10:AF10"/>
-    <mergeCell ref="AE12:AF12"/>
-    <mergeCell ref="AE14:AF14"/>
-    <mergeCell ref="AE15:AF15"/>
-    <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="D4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="AH4:AI5"/>
+    <mergeCell ref="T6:X6"/>
+    <mergeCell ref="AH8:AI8"/>
+    <mergeCell ref="AH10:AI10"/>
+    <mergeCell ref="AH12:AI12"/>
+    <mergeCell ref="AH14:AI14"/>
+    <mergeCell ref="AH15:AI15"/>
+    <mergeCell ref="AH16:AI16"/>
   </mergeCells>
-  <conditionalFormatting sqref="AE13">
+  <conditionalFormatting sqref="AH13">
     <cfRule type="iconSet" priority="5">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
@@ -5775,7 +6000,7 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE16">
+  <conditionalFormatting sqref="AH16">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
@@ -5793,7 +6018,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="greaterThan" id="{D478FF37-DC40-4A02-8AC8-3442060AC61F}">
+          <x14:cfRule type="cellIs" priority="3" operator="greaterThan" id="{F8FDA914-5C60-4A0B-B07B-0D04611CD3EC}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5807,10 +6032,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>AC8:AC13</xm:sqref>
+          <xm:sqref>AF8:AF13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="lessThan" id="{E7556649-089B-4527-AC7A-3C75D0A5AD79}">
+          <x14:cfRule type="cellIs" priority="4" operator="lessThan" id="{759F7621-B54C-4C24-9011-4AC89B5382FB}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -5824,7 +6049,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>AC8:AC13</xm:sqref>
+          <xm:sqref>AF8:AF13</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5840,8 +6065,8 @@
     <col customWidth="1" min="3" max="3" width="4.25"/>
     <col customWidth="1" min="13" max="14" width="13.5"/>
     <col customWidth="1" min="15" max="15" width="4"/>
-    <col customWidth="1" min="16" max="17" style="139" width="17.375"/>
-    <col customWidth="1" min="18" max="18" style="36" width="13.875"/>
+    <col customWidth="1" min="16" max="17" style="142" width="17.375"/>
+    <col customWidth="1" min="18" max="18" style="41" width="13.875"/>
     <col customWidth="1" min="19" max="19" width="2.5"/>
     <col customWidth="1" min="20" max="20" width="15.875"/>
     <col customWidth="1" min="21" max="21" width="16.875"/>
@@ -5849,613 +6074,613 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="B1" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
+      <c r="B1" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
     </row>
     <row r="2" ht="16.5" customHeight="1">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
     </row>
     <row r="4" ht="16.5">
-      <c r="B4" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="42" t="s">
+      <c r="B4" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="N4" s="49"/>
+      <c r="P4" s="150"/>
+      <c r="Q4" s="151"/>
+      <c r="R4" s="152"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="52" t="s">
+        <v>152</v>
+      </c>
+      <c r="U4" s="53"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="B5" s="54"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="K5" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="M5" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="N5" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="P5" s="153" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q5" s="154" t="s">
+        <v>157</v>
+      </c>
+      <c r="R5" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="S5" s="51"/>
+      <c r="T5" s="66"/>
+      <c r="U5" s="67"/>
+    </row>
+    <row r="6" ht="16.5">
+      <c r="B6" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="69" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="L6" s="155"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="71"/>
+      <c r="P6" s="156"/>
+      <c r="Q6" s="156"/>
+      <c r="R6" s="157"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="81"/>
+      <c r="U6" s="81"/>
+    </row>
+    <row r="7" ht="16.5">
+      <c r="B7" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="N4" s="44"/>
-      <c r="P4" s="141"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="143"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="U4" s="48"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="B5" s="49"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="I5" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="J5" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="K5" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="L5" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="M5" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="N5" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="P5" s="144" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q5" s="145" t="s">
-        <v>145</v>
-      </c>
-      <c r="R5" s="146" t="s">
-        <v>146</v>
-      </c>
-      <c r="S5" s="46"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="62"/>
-    </row>
-    <row r="6" ht="16.5">
-      <c r="B6" s="63" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="L6" s="147"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="66"/>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="148"/>
-      <c r="R6" s="149"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="76"/>
-      <c r="U6" s="76"/>
-    </row>
-    <row r="7" ht="16.5">
-      <c r="B7" s="63" t="s">
-        <v>130</v>
-      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="86">
+      <c r="D7" s="91">
         <v>874</v>
       </c>
-      <c r="E7" s="87">
+      <c r="E7" s="92">
         <v>527</v>
       </c>
-      <c r="F7" s="87">
-        <v>0</v>
-      </c>
-      <c r="G7" s="87">
-        <v>0</v>
-      </c>
-      <c r="H7" s="87">
-        <v>0</v>
-      </c>
-      <c r="I7" s="87">
+      <c r="F7" s="92">
+        <v>0</v>
+      </c>
+      <c r="G7" s="92">
+        <v>0</v>
+      </c>
+      <c r="H7" s="92">
+        <v>0</v>
+      </c>
+      <c r="I7" s="92">
         <v>570</v>
       </c>
-      <c r="J7" s="87">
-        <v>0</v>
-      </c>
-      <c r="K7" s="87">
-        <v>0</v>
-      </c>
-      <c r="L7" s="147"/>
-      <c r="M7" s="90">
+      <c r="J7" s="92">
+        <v>0</v>
+      </c>
+      <c r="K7" s="92">
+        <v>0</v>
+      </c>
+      <c r="L7" s="155"/>
+      <c r="M7" s="95">
         <v>642</v>
       </c>
-      <c r="N7" s="93">
+      <c r="N7" s="98">
         <v>5232</v>
       </c>
-      <c r="P7" s="97">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="97">
-        <v>0</v>
-      </c>
-      <c r="R7" s="150">
+      <c r="P7" s="102">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="102">
+        <v>0</v>
+      </c>
+      <c r="R7" s="158">
         <v>116616.82000000001</v>
       </c>
-      <c r="S7" s="46"/>
-      <c r="T7" s="98" t="s">
-        <v>147</v>
-      </c>
-      <c r="U7" s="99"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="103" t="s">
+        <v>159</v>
+      </c>
+      <c r="U7" s="104"/>
     </row>
     <row r="8" ht="16.5">
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="86">
+      <c r="D8" s="91">
         <v>1091</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="92">
         <v>949</v>
       </c>
-      <c r="F8" s="87">
-        <v>0</v>
-      </c>
-      <c r="G8" s="87">
+      <c r="F8" s="92">
+        <v>0</v>
+      </c>
+      <c r="G8" s="92">
         <v>780</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="92">
         <v>7</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="92">
         <v>251</v>
       </c>
-      <c r="J8" s="87">
-        <v>0</v>
-      </c>
-      <c r="K8" s="87">
+      <c r="J8" s="92">
+        <v>0</v>
+      </c>
+      <c r="K8" s="92">
         <v>1575</v>
       </c>
-      <c r="L8" s="147"/>
-      <c r="M8" s="90">
+      <c r="L8" s="155"/>
+      <c r="M8" s="95">
         <v>5048</v>
       </c>
-      <c r="N8" s="93">
+      <c r="N8" s="98">
         <v>17738</v>
       </c>
-      <c r="P8" s="100">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="100">
-        <v>0</v>
-      </c>
-      <c r="R8" s="150">
+      <c r="P8" s="105">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="105">
+        <v>0</v>
+      </c>
+      <c r="R8" s="158">
         <v>211853.97</v>
       </c>
-      <c r="S8" s="46"/>
-      <c r="T8" s="101"/>
-      <c r="U8" s="102"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="106"/>
+      <c r="U8" s="107"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="68" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="103">
-        <f t="shared" ref="D9:D10" si="21">1575*0.6</f>
+      <c r="D9" s="108">
+        <f t="shared" ref="D9:D10" si="24">1575*0.6</f>
         <v>945</v>
       </c>
-      <c r="E9" s="104">
-        <v>0</v>
-      </c>
-      <c r="F9" s="104">
+      <c r="E9" s="109">
+        <v>0</v>
+      </c>
+      <c r="F9" s="109">
         <v>1575</v>
       </c>
-      <c r="G9" s="104">
-        <f t="shared" ref="G9:G10" si="22">1575*0.7</f>
+      <c r="G9" s="109">
+        <f t="shared" ref="G9:G10" si="25">1575*0.7</f>
         <v>1102.5</v>
       </c>
-      <c r="H9" s="104">
-        <v>0</v>
-      </c>
-      <c r="I9" s="104">
-        <v>0</v>
-      </c>
-      <c r="J9" s="104">
+      <c r="H9" s="109">
+        <v>0</v>
+      </c>
+      <c r="I9" s="109">
+        <v>0</v>
+      </c>
+      <c r="J9" s="109">
         <v>787</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="109">
         <v>120</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="108">
         <f>SUM(D9:K9)</f>
         <v>4529.5</v>
       </c>
-      <c r="M9" s="106">
+      <c r="M9" s="111">
         <v>32492</v>
       </c>
-      <c r="N9" s="109">
+      <c r="N9" s="114">
         <v>32492</v>
       </c>
-      <c r="P9" s="110">
+      <c r="P9" s="115">
         <f>((((D9*Rates!$E$25)+('June  26 - UKRI'!F9*Rates!$E$24)+(('June  26 - UKRI'!G9+'June  26 - UKRI'!K9)*Rates!$E$23)+('June  26 - UKRI'!J9*Rates!$E$16))*Rates!$I$11)*0.8)+M9+N9</f>
         <v>324242.73791999999</v>
       </c>
-      <c r="Q9" s="110">
+      <c r="Q9" s="115">
         <f>((((E9*Rates!$E$25)+('June  26 - UKRI'!G9*Rates!$E$24)+(('June  26 - UKRI'!H9+'June  26 - UKRI'!L9)*Rates!$E$23)+('June  26 - UKRI'!K9*Rates!$E$16))*Rates!$I$11)*0.2)</f>
         <v>71705.037039999996</v>
       </c>
-      <c r="R9" s="151">
+      <c r="R9" s="159">
         <v>43314</v>
       </c>
-      <c r="S9" s="46"/>
-      <c r="T9" s="112">
+      <c r="S9" s="51"/>
+      <c r="T9" s="117">
         <v>1605398</v>
       </c>
-      <c r="U9" s="113"/>
+      <c r="U9" s="118"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="68" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="103">
-        <f t="shared" si="21"/>
+      <c r="D10" s="108">
+        <f t="shared" si="24"/>
         <v>945</v>
       </c>
-      <c r="E10" s="104">
-        <v>0</v>
-      </c>
-      <c r="F10" s="104">
+      <c r="E10" s="109">
+        <v>0</v>
+      </c>
+      <c r="F10" s="109">
         <v>1575</v>
       </c>
-      <c r="G10" s="104">
-        <f t="shared" si="22"/>
+      <c r="G10" s="109">
+        <f t="shared" si="25"/>
         <v>1102.5</v>
       </c>
-      <c r="H10" s="104">
-        <v>0</v>
-      </c>
-      <c r="I10" s="104">
-        <v>0</v>
-      </c>
-      <c r="J10" s="104">
+      <c r="H10" s="109">
+        <v>0</v>
+      </c>
+      <c r="I10" s="109">
+        <v>0</v>
+      </c>
+      <c r="J10" s="109">
         <v>1575</v>
       </c>
-      <c r="K10" s="104">
-        <v>0</v>
-      </c>
-      <c r="L10" s="103">
-        <f t="shared" ref="L10:L11" si="23">SUM(D10:K10)</f>
+      <c r="K10" s="109">
+        <v>0</v>
+      </c>
+      <c r="L10" s="108">
+        <f t="shared" ref="L10:L11" si="26">SUM(D10:K10)</f>
         <v>5197.5</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="111">
         <v>32492</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="114">
         <v>32492</v>
       </c>
-      <c r="P10" s="110">
+      <c r="P10" s="115">
         <f>((((D10*Rates!$F$25)+('June  26 - UKRI'!F10*Rates!$F$24)+(('June  26 - UKRI'!G10+'June  26 - UKRI'!K10)*Rates!$F$23)+('June  26 - UKRI'!J10*Rates!$F$16))*Rates!$I$11)*0.8)+M10+N10</f>
         <v>358188.95626240002</v>
       </c>
-      <c r="Q10" s="110">
+      <c r="Q10" s="115">
         <f>((((E10*Rates!$F$25)+('June  26 - UKRI'!G10*Rates!$F$24)+(('June  26 - UKRI'!H10+'June  26 - UKRI'!L10)*Rates!$F$23)+('June  26 - UKRI'!K10*Rates!$F$16))*Rates!$I$11)*0.2)</f>
         <v>81625.114771199995</v>
       </c>
-      <c r="R10" s="151"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="114"/>
-      <c r="U10" s="114"/>
+      <c r="R10" s="159"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="119"/>
+      <c r="U10" s="119"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="68" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="103">
+      <c r="D11" s="108">
         <f>((1575/12)*3)*0.6</f>
         <v>236.25</v>
       </c>
-      <c r="E11" s="104">
-        <v>0</v>
-      </c>
-      <c r="F11" s="104">
+      <c r="E11" s="109">
+        <v>0</v>
+      </c>
+      <c r="F11" s="109">
         <f>(1575/12)*3</f>
         <v>393.75</v>
       </c>
-      <c r="G11" s="89">
+      <c r="G11" s="94">
         <f>((1575/12)*3)*0.7</f>
         <v>275.625</v>
       </c>
-      <c r="H11" s="89">
-        <v>0</v>
-      </c>
-      <c r="I11" s="89">
-        <v>0</v>
-      </c>
-      <c r="J11" s="104">
+      <c r="H11" s="94">
+        <v>0</v>
+      </c>
+      <c r="I11" s="94">
+        <v>0</v>
+      </c>
+      <c r="J11" s="109">
         <f>(1575/12)*3</f>
         <v>393.75</v>
       </c>
-      <c r="K11" s="104">
-        <v>0</v>
-      </c>
-      <c r="L11" s="103">
-        <f t="shared" si="23"/>
+      <c r="K11" s="109">
+        <v>0</v>
+      </c>
+      <c r="L11" s="108">
+        <f t="shared" si="26"/>
         <v>1299.375</v>
       </c>
-      <c r="M11" s="106">
+      <c r="M11" s="111">
         <v>29555</v>
       </c>
-      <c r="N11" s="109">
+      <c r="N11" s="114">
         <v>29555</v>
       </c>
-      <c r="P11" s="110">
+      <c r="P11" s="115">
         <f>((((D11*Rates!$G$25)+('June  26 - UKRI'!F11*Rates!$G$24)+(('June  26 - UKRI'!G11+'June  26 - UKRI'!K11)*Rates!$G$23)+('June  26 - UKRI'!J11*Rates!$G$16))*Rates!$I$11)*0.8)+M11+N11</f>
         <v>135343.28862822402</v>
       </c>
-      <c r="Q11" s="110">
+      <c r="Q11" s="115">
         <f>((((E11*Rates!$G$25)+('June  26 - UKRI'!G11*Rates!$G$24)+(('June  26 - UKRI'!H11+'June  26 - UKRI'!L11)*Rates!$G$23)+('June  26 - UKRI'!K11*Rates!$G$16))*Rates!$I$11)*0.2)</f>
         <v>21222.529840512005</v>
       </c>
-      <c r="R11" s="151"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="152" t="s">
-        <v>132</v>
-      </c>
-      <c r="U11" s="153"/>
+      <c r="R11" s="159"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="U11" s="104"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="154"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="89"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="109"/>
-      <c r="P12" s="110"/>
-      <c r="Q12" s="110"/>
-      <c r="R12" s="151"/>
-      <c r="S12" s="122"/>
-      <c r="T12" s="155"/>
-      <c r="U12" s="156"/>
+      <c r="B12" s="160"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="114"/>
+      <c r="P12" s="115"/>
+      <c r="Q12" s="115"/>
+      <c r="R12" s="159"/>
+      <c r="S12" s="125"/>
+      <c r="T12" s="161"/>
+      <c r="U12" s="162"/>
     </row>
     <row r="13" ht="24.75">
-      <c r="B13" s="125" t="s">
-        <v>133</v>
+      <c r="B13" s="127" t="s">
+        <v>142</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="126">
+      <c r="D13" s="128">
         <f>SUM(D7:D12)</f>
         <v>4091.25</v>
       </c>
-      <c r="E13" s="127">
-        <f t="shared" ref="E13:K13" si="24">SUM(E7:E12)</f>
+      <c r="E13" s="129">
+        <f t="shared" ref="E13:K13" si="27">SUM(E7:E12)</f>
         <v>1476</v>
       </c>
-      <c r="F13" s="127">
-        <f t="shared" si="24"/>
+      <c r="F13" s="129">
+        <f t="shared" si="27"/>
         <v>3543.75</v>
       </c>
-      <c r="G13" s="127">
-        <f t="shared" si="24"/>
+      <c r="G13" s="129">
+        <f t="shared" si="27"/>
         <v>3260.625</v>
       </c>
-      <c r="H13" s="127">
-        <f t="shared" si="24"/>
+      <c r="H13" s="129">
+        <f t="shared" si="27"/>
         <v>7</v>
       </c>
-      <c r="I13" s="127">
-        <f t="shared" si="24"/>
+      <c r="I13" s="129">
+        <f t="shared" si="27"/>
         <v>821</v>
       </c>
-      <c r="J13" s="127">
-        <f t="shared" si="24"/>
+      <c r="J13" s="129">
+        <f t="shared" si="27"/>
         <v>2755.75</v>
       </c>
-      <c r="K13" s="127">
-        <f t="shared" si="24"/>
+      <c r="K13" s="129">
+        <f t="shared" si="27"/>
         <v>1695</v>
       </c>
-      <c r="L13" s="126">
+      <c r="L13" s="128">
         <f>SUM(L9:L12)</f>
         <v>11026.375</v>
       </c>
-      <c r="M13" s="129">
+      <c r="M13" s="131">
         <f>SUM(M7:M12)</f>
         <v>100229</v>
       </c>
-      <c r="N13" s="131">
+      <c r="N13" s="133">
         <f>SUM(N7:N12)</f>
         <v>117509</v>
       </c>
-      <c r="P13" s="132">
+      <c r="P13" s="134">
         <f>SUM(P7:P11)</f>
         <v>817774.98281062406</v>
       </c>
-      <c r="Q13" s="132">
+      <c r="Q13" s="134">
         <f>SUM(Q7:Q11)</f>
         <v>174552.68165171199</v>
       </c>
-      <c r="R13" s="157">
+      <c r="R13" s="163">
         <f>SUM(R7:R12)</f>
         <v>371784.79000000004</v>
       </c>
-      <c r="S13" s="122"/>
-      <c r="T13" s="112">
+      <c r="S13" s="125"/>
+      <c r="T13" s="117">
         <f>(P13-R9)+R13</f>
         <v>1146245.772810624</v>
       </c>
-      <c r="U13" s="113"/>
+      <c r="U13" s="118"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="S14" s="122"/>
+      <c r="S14" s="125"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="P15" s="138"/>
       <c r="Q15" s="138"/>
-      <c r="S15" s="122"/>
-      <c r="T15" s="152" t="s">
-        <v>148</v>
-      </c>
-      <c r="U15" s="153"/>
+      <c r="S15" s="125"/>
+      <c r="T15" s="103" t="s">
+        <v>160</v>
+      </c>
+      <c r="U15" s="104"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="P16" s="158"/>
-      <c r="S16" s="122"/>
-      <c r="T16" s="155"/>
-      <c r="U16" s="156"/>
+      <c r="P16" s="141"/>
+      <c r="S16" s="125"/>
+      <c r="T16" s="161"/>
+      <c r="U16" s="162"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="P17" s="138"/>
       <c r="Q17" s="138"/>
-      <c r="S17" s="122"/>
-      <c r="T17" s="112">
+      <c r="S17" s="125"/>
+      <c r="T17" s="117">
         <f>T9-T13</f>
         <v>459152.22718937602</v>
       </c>
-      <c r="U17" s="113"/>
+      <c r="U17" s="118"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="M18" s="159"/>
-      <c r="N18" s="159"/>
+      <c r="M18" s="164"/>
+      <c r="N18" s="164"/>
       <c r="P18" s="138"/>
       <c r="Q18" s="138"/>
-      <c r="S18" s="122"/>
-      <c r="T18" s="160"/>
-      <c r="U18" s="160"/>
+      <c r="S18" s="125"/>
+      <c r="T18" s="165"/>
+      <c r="U18" s="165"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="M19" s="159"/>
-      <c r="N19" s="159"/>
-      <c r="O19" s="161"/>
+      <c r="M19" s="164"/>
+      <c r="N19" s="164"/>
+      <c r="O19" s="145"/>
       <c r="P19"/>
       <c r="Q19"/>
-      <c r="S19" s="122"/>
+      <c r="S19" s="125"/>
       <c r="T19" s="137"/>
       <c r="U19" s="137"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="M20" s="159"/>
-      <c r="N20" s="159"/>
-      <c r="O20" s="161"/>
+      <c r="M20" s="164"/>
+      <c r="N20" s="164"/>
+      <c r="O20" s="145"/>
       <c r="P20" s="138"/>
       <c r="Q20" s="138"/>
-      <c r="S20" s="122"/>
+      <c r="S20" s="125"/>
       <c r="T20" s="137"/>
       <c r="U20" s="137"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="P21" s="162"/>
-      <c r="Q21" s="162"/>
-      <c r="R21" s="163"/>
-      <c r="S21" s="163"/>
-      <c r="T21" s="163"/>
-      <c r="U21" s="163"/>
-      <c r="V21" s="163"/>
-      <c r="W21" s="163"/>
-      <c r="X21" s="163"/>
-      <c r="Y21" s="163"/>
-      <c r="Z21" s="163"/>
+      <c r="P21" s="146"/>
+      <c r="Q21" s="146"/>
+      <c r="R21" s="148"/>
+      <c r="S21" s="148"/>
+      <c r="T21" s="148"/>
+      <c r="U21" s="148"/>
+      <c r="V21" s="148"/>
+      <c r="W21" s="148"/>
+      <c r="X21" s="148"/>
+      <c r="Y21" s="148"/>
+      <c r="Z21" s="148"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="P22" s="163"/>
-      <c r="Q22" s="163"/>
-      <c r="R22" s="163"/>
-      <c r="S22" s="163"/>
-      <c r="T22" s="163"/>
-      <c r="U22" s="163"/>
-      <c r="V22" s="163"/>
-      <c r="W22" s="163"/>
-      <c r="X22" s="163"/>
-      <c r="Y22" s="163"/>
-      <c r="Z22" s="163"/>
+      <c r="P22" s="148"/>
+      <c r="Q22" s="148"/>
+      <c r="R22" s="148"/>
+      <c r="S22" s="148"/>
+      <c r="T22" s="148"/>
+      <c r="U22" s="148"/>
+      <c r="V22" s="148"/>
+      <c r="W22" s="148"/>
+      <c r="X22" s="148"/>
+      <c r="Y22" s="148"/>
+      <c r="Z22" s="148"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="S23" s="122"/>
-      <c r="U23" s="164"/>
+      <c r="S23" s="125"/>
+      <c r="U23" s="166"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="S24" s="122"/>
+      <c r="S24" s="125"/>
       <c r="T24" s="137"/>
       <c r="U24" s="137"/>
     </row>
@@ -6464,9 +6689,9 @@
       <c r="U25" s="137"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="S26" s="122"/>
-      <c r="T26" s="165"/>
-      <c r="U26" s="165"/>
+      <c r="S26" s="125"/>
+      <c r="T26" s="167"/>
+      <c r="U26" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -6525,7 +6750,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="greaterThan" id="{3AF710B0-12F0-47BE-BE07-BB660430AD47}">
+          <x14:cfRule type="cellIs" priority="4" operator="greaterThan" id="{F9EB759D-3574-4FE7-B0E4-8086AD22A3E2}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -6542,7 +6767,7 @@
           <xm:sqref>R7:R12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{C10C15E7-7821-4831-A6BD-9975C375901B}">
+          <x14:cfRule type="cellIs" priority="5" operator="lessThan" id="{6A8C9275-C961-4A0D-B513-D66E2447C070}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -6568,694 +6793,935 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="13.625"/>
+    <col customWidth="1" hidden="1" min="1" max="1" width="0"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="7.63671875"/>
     <col customWidth="1" min="3" max="3" width="4.25"/>
-    <col min="4" max="5" width="9"/>
-    <col min="8" max="8" width="9"/>
-    <col min="12" max="12" width="9"/>
-    <col customWidth="1" min="14" max="15" width="13.5"/>
-    <col customWidth="1" min="16" max="16" width="4"/>
-    <col customWidth="1" min="17" max="18" style="139" width="17.375"/>
-    <col customWidth="1" min="19" max="19" style="36" width="13.875"/>
-    <col customWidth="1" min="20" max="20" width="2.5"/>
-    <col customWidth="1" min="21" max="21" width="15.875"/>
-    <col customWidth="1" min="22" max="22" width="16.875"/>
-    <col customWidth="1" min="23" max="23" width="3.375"/>
+    <col customWidth="1" min="4" max="15" width="6.77734375"/>
+    <col customWidth="1" min="16" max="16" width="7.6640625"/>
+    <col customWidth="1" min="17" max="18" width="13.5"/>
+    <col customWidth="1" min="19" max="19" width="4"/>
+    <col customWidth="1" min="20" max="21" style="142" width="17.375"/>
+    <col customWidth="1" min="22" max="22" style="41" width="13.875"/>
+    <col customWidth="1" min="23" max="23" width="2.5"/>
+    <col customWidth="1" min="24" max="24" width="15.875"/>
+    <col customWidth="1" min="25" max="25" width="16.875"/>
+    <col customWidth="1" min="26" max="26" width="3.375"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="B1" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
+      <c r="B1" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
     </row>
     <row r="2" ht="16.5" customHeight="1">
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
     </row>
     <row r="4" ht="16.5">
-      <c r="B4" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="140"/>
-      <c r="N4" s="42" t="s">
+      <c r="B4" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="R4" s="49"/>
+      <c r="T4" s="150"/>
+      <c r="U4" s="151"/>
+      <c r="V4" s="152"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="52" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y4" s="53"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="B5" s="54"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="K5" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="L5" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="M5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="N5" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="O5" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="P5" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q5" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="R5" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="T5" s="153" t="s">
+        <v>156</v>
+      </c>
+      <c r="U5" s="154" t="s">
+        <v>157</v>
+      </c>
+      <c r="V5" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="W5" s="51"/>
+      <c r="X5" s="66"/>
+      <c r="Y5" s="67"/>
+    </row>
+    <row r="6" ht="16.5">
+      <c r="B6" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="69" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="70" t="s">
+        <v>165</v>
+      </c>
+      <c r="J6" s="70" t="s">
+        <v>165</v>
+      </c>
+      <c r="K6" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="M6" s="70" t="s">
+        <v>165</v>
+      </c>
+      <c r="N6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="O6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="P6" s="155"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="71"/>
+      <c r="T6" s="156"/>
+      <c r="U6" s="156"/>
+      <c r="V6" s="157"/>
+      <c r="W6" s="51"/>
+      <c r="X6" s="81"/>
+      <c r="Y6" s="81"/>
+    </row>
+    <row r="7" ht="16.5">
+      <c r="B7" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="Q4" s="141"/>
-      <c r="R4" s="142"/>
-      <c r="S4" s="143"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="V4" s="48"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="B5" s="49"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H5" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="I5" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="J5" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="K5" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="M5" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="N5" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="O5" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q5" s="144" t="s">
-        <v>144</v>
-      </c>
-      <c r="R5" s="145" t="s">
-        <v>145</v>
-      </c>
-      <c r="S5" s="146" t="s">
-        <v>146</v>
-      </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="61"/>
-      <c r="V5" s="62"/>
-    </row>
-    <row r="6" ht="16.5">
-      <c r="B6" s="63" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="H6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="M6" s="147"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="66"/>
-      <c r="Q6" s="148"/>
-      <c r="R6" s="148"/>
-      <c r="S6" s="149"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="76"/>
-      <c r="V6" s="76"/>
-    </row>
-    <row r="7" ht="16.5">
-      <c r="B7" s="63" t="s">
-        <v>130</v>
-      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="86">
+      <c r="D7" s="91">
         <v>874</v>
       </c>
-      <c r="E7" s="87">
+      <c r="E7" s="92">
         <v>527</v>
       </c>
-      <c r="F7" s="87">
-        <v>0</v>
-      </c>
-      <c r="G7" s="87">
-        <v>0</v>
-      </c>
-      <c r="H7" s="87">
-        <v>0</v>
-      </c>
-      <c r="I7" s="87">
-        <v>0</v>
-      </c>
-      <c r="J7" s="87">
+      <c r="F7" s="92">
+        <v>0</v>
+      </c>
+      <c r="G7" s="92">
+        <v>0</v>
+      </c>
+      <c r="H7" s="92">
+        <v>0</v>
+      </c>
+      <c r="I7" s="92">
+        <v>0</v>
+      </c>
+      <c r="J7" s="92">
         <v>570</v>
       </c>
-      <c r="K7" s="87">
-        <v>0</v>
-      </c>
-      <c r="L7" s="87">
-        <v>0</v>
-      </c>
-      <c r="M7" s="147"/>
-      <c r="N7" s="90">
+      <c r="K7" s="92">
+        <v>0</v>
+      </c>
+      <c r="L7" s="92">
+        <v>0</v>
+      </c>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92">
+        <v>0</v>
+      </c>
+      <c r="O7" s="92">
+        <v>0</v>
+      </c>
+      <c r="P7" s="155"/>
+      <c r="Q7" s="95">
         <v>642</v>
       </c>
-      <c r="O7" s="93">
+      <c r="R7" s="98">
         <v>5232</v>
       </c>
-      <c r="Q7" s="97">
-        <v>0</v>
-      </c>
-      <c r="R7" s="97">
-        <v>0</v>
-      </c>
-      <c r="S7" s="150">
+      <c r="T7" s="102">
+        <v>0</v>
+      </c>
+      <c r="U7" s="102">
+        <v>0</v>
+      </c>
+      <c r="V7" s="158">
         <v>116616.82000000001</v>
       </c>
-      <c r="T7" s="46"/>
-      <c r="U7" s="98" t="s">
-        <v>147</v>
-      </c>
-      <c r="V7" s="99"/>
+      <c r="W7" s="51"/>
+      <c r="X7" s="103" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y7" s="104"/>
     </row>
     <row r="8" ht="16.5">
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="86">
+      <c r="D8" s="91">
         <v>1091</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="92">
         <v>949</v>
       </c>
-      <c r="F8" s="87">
-        <v>0</v>
-      </c>
-      <c r="G8" s="87">
+      <c r="F8" s="92">
+        <v>0</v>
+      </c>
+      <c r="G8" s="92">
         <v>780</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="92">
         <v>780</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="92">
         <v>7</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="92">
         <v>251</v>
       </c>
-      <c r="K8" s="87">
-        <v>0</v>
-      </c>
-      <c r="L8" s="87">
-        <v>1575</v>
-      </c>
-      <c r="M8" s="147"/>
-      <c r="N8" s="90">
+      <c r="K8" s="92">
+        <v>0</v>
+      </c>
+      <c r="L8" s="92">
+        <f>1575/2*3/5</f>
+        <v>472.5</v>
+      </c>
+      <c r="M8" s="92"/>
+      <c r="N8" s="92">
+        <v>0</v>
+      </c>
+      <c r="O8" s="92">
+        <v>0</v>
+      </c>
+      <c r="P8" s="155"/>
+      <c r="Q8" s="95">
         <v>5048</v>
       </c>
-      <c r="O8" s="93">
+      <c r="R8" s="98">
         <v>17738</v>
       </c>
-      <c r="Q8" s="100">
-        <v>0</v>
-      </c>
-      <c r="R8" s="100">
-        <v>0</v>
-      </c>
-      <c r="S8" s="150">
+      <c r="T8" s="105">
+        <v>0</v>
+      </c>
+      <c r="U8" s="105">
+        <v>0</v>
+      </c>
+      <c r="V8" s="158">
         <v>211853.97</v>
       </c>
-      <c r="T8" s="46"/>
-      <c r="U8" s="101"/>
-      <c r="V8" s="102"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="106"/>
+      <c r="Y8" s="107"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="68" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="103">
-        <f t="shared" ref="D9:D10" si="25">1575*0.6</f>
+      <c r="D9" s="108">
+        <f t="shared" ref="D9:D10" si="28">1575*0.6</f>
         <v>945</v>
       </c>
-      <c r="E9" s="104">
-        <v>0</v>
-      </c>
-      <c r="F9" s="104">
-        <v>1575</v>
-      </c>
-      <c r="G9" s="104">
-        <f>1575*0.7</f>
-        <v>1102.5</v>
-      </c>
-      <c r="H9" s="104">
-        <f>1575*0.7</f>
-        <v>1102.5</v>
-      </c>
-      <c r="I9" s="104">
-        <v>0</v>
-      </c>
-      <c r="J9" s="104">
-        <v>0</v>
-      </c>
-      <c r="K9" s="166">
+      <c r="E9" s="109">
+        <f>1575*6/12</f>
+        <v>787.5</v>
+      </c>
+      <c r="F9" s="109">
+        <f>1575*6/12</f>
+        <v>787.5</v>
+      </c>
+      <c r="G9" s="109">
+        <f>1575*6/12*0.7</f>
+        <v>551.25</v>
+      </c>
+      <c r="H9" s="109">
+        <f>1575*6/12*0.7</f>
+        <v>551.25</v>
+      </c>
+      <c r="I9" s="109">
+        <v>0</v>
+      </c>
+      <c r="J9" s="109">
+        <v>0</v>
+      </c>
+      <c r="K9" s="109">
         <f>787*2</f>
         <v>1574</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="109">
         <f>1575*6/12*3/5</f>
         <v>472.5</v>
       </c>
-      <c r="M9" s="103">
-        <f>SUM(D9:L9)</f>
-        <v>6771.5</v>
-      </c>
-      <c r="N9" s="106">
-        <v>32492</v>
+      <c r="M9" s="109">
+        <f>2*1575*9/12</f>
+        <v>2362.5</v>
+      </c>
+      <c r="N9" s="109">
+        <f>1575*6/12*0.6</f>
+        <v>472.5</v>
       </c>
       <c r="O9" s="109">
-        <v>32492</v>
-      </c>
-      <c r="Q9" s="110">
-        <f>((((D9*Rates!$E$25)+(UKRI!F9*Rates!$E$24)+((UKRI!H9+UKRI!L9)*Rates!$E$23)+(UKRI!K9*Rates!$E$16))*Rates!$I$11)*0.8)+N9+O9</f>
-        <v>369110.77568000002</v>
-      </c>
-      <c r="R9" s="110">
-        <f>((((E9*Rates!$E$25)+(UKRI!H9*Rates!$E$24)+((UKRI!I9+UKRI!M9)*Rates!$E$23)+(UKRI!L9*Rates!$E$16))*Rates!$I$11)*0.2)</f>
-        <v>101247.69199999998</v>
-      </c>
-      <c r="S9" s="151">
+        <f>1575*8/12*0.4</f>
+        <v>420</v>
+      </c>
+      <c r="P9" s="108">
+        <f>SUM(D9:O9)</f>
+        <v>8924</v>
+      </c>
+      <c r="Q9" s="111">
+        <v>6000</v>
+      </c>
+      <c r="R9" s="114">
+        <v>20000</v>
+      </c>
+      <c r="T9" s="115">
+        <f>(((((D9*Rates!$E$25)+(UKRI!E9*Rates!$E$23)+(UKRI!F9*Rates!$E$24)+(UKRI!G9*Rates!$E$23)+(UKRI!H9*Rates!$J$22)+(UKRI!K9*Rates!$E$16)+(UKRI!L9*Rates!$E$23)+(UKRI!M9*Rates!$J$25)+(UKRI!N9*Rates!$E$23)+(UKRI!O9*Rates!$E$23))*Rates!$I$11)+Q9+R9)*0.8)</f>
+        <v>398812.05175999994</v>
+      </c>
+      <c r="U9" s="115">
+        <f>T9/0.8*0.2</f>
+        <v>99703.012939999986</v>
+      </c>
+      <c r="V9" s="159">
         <v>43314</v>
       </c>
-      <c r="T9" s="46"/>
-      <c r="U9" s="112">
+      <c r="W9" s="51"/>
+      <c r="X9" s="117">
         <v>1605398</v>
       </c>
-      <c r="V9" s="113"/>
+      <c r="Y9" s="118"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="68" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="103">
-        <f t="shared" si="25"/>
+      <c r="D10" s="108">
+        <f t="shared" si="28"/>
         <v>945</v>
       </c>
-      <c r="E10" s="104">
-        <v>0</v>
-      </c>
-      <c r="F10" s="104">
+      <c r="E10" s="109">
+        <v>0</v>
+      </c>
+      <c r="F10" s="109">
         <v>1575</v>
       </c>
-      <c r="G10" s="104">
+      <c r="G10" s="109">
+        <v>0</v>
+      </c>
+      <c r="H10" s="109">
         <v>1575</v>
       </c>
-      <c r="H10" s="104">
-        <v>1575</v>
-      </c>
-      <c r="I10" s="104">
-        <v>0</v>
-      </c>
-      <c r="J10" s="104">
-        <v>0</v>
-      </c>
-      <c r="K10" s="104">
+      <c r="I10" s="109">
+        <v>0</v>
+      </c>
+      <c r="J10" s="109">
+        <v>0</v>
+      </c>
+      <c r="K10" s="109">
         <f>1575*2</f>
         <v>3150</v>
       </c>
-      <c r="L10" s="104">
-        <v>0</v>
-      </c>
-      <c r="M10" s="103">
-        <f>SUM(D10:L10)</f>
-        <v>8820</v>
-      </c>
-      <c r="N10" s="106">
-        <v>32492</v>
+      <c r="L10" s="109">
+        <v>0</v>
+      </c>
+      <c r="M10" s="109">
+        <f>2*1575*3/12</f>
+        <v>787.5</v>
+      </c>
+      <c r="N10" s="109">
+        <v>0</v>
       </c>
       <c r="O10" s="109">
-        <v>32492</v>
-      </c>
-      <c r="Q10" s="110">
-        <f>((((D10*Rates!$F$25)+(UKRI!F10*Rates!$F$24)+((UKRI!H10+UKRI!L10)*Rates!$F$23)+(UKRI!K10*Rates!$F$16))*Rates!$I$11)*0.8)+N10+O10</f>
-        <v>440173.24119039997</v>
-      </c>
-      <c r="R10" s="110">
-        <f>((((E10*Rates!$F$25)+(UKRI!H10*Rates!$F$24)+((UKRI!I10+UKRI!M10)*Rates!$F$23)+(UKRI!L10*Rates!$F$16))*Rates!$I$11)*0.2)</f>
-        <v>133675.21440000003</v>
-      </c>
-      <c r="S10" s="151"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="114"/>
-      <c r="V10" s="114"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="108">
+        <f t="shared" ref="P10:P11" si="29">SUM(D10:O10)</f>
+        <v>8032.5</v>
+      </c>
+      <c r="Q10" s="111">
+        <v>6000</v>
+      </c>
+      <c r="R10" s="114">
+        <v>20000</v>
+      </c>
+      <c r="T10" s="115">
+        <f>(((((D10*Rates!$F$25)+(UKRI!E10*Rates!$F$23)+(UKRI!F10*Rates!$F$24)+(UKRI!G10*Rates!$F$23)+(UKRI!H10*Rates!$K$22)+(UKRI!K10*Rates!$F$16)+(UKRI!L10*Rates!$F$23)+(UKRI!M10*Rates!$K$25)+(UKRI!N10*Rates!$F$23)+(UKRI!O10*Rates!$F$23))*Rates!$I$11)+Q10+R10)*0.8)</f>
+        <v>422839.73322240007</v>
+      </c>
+      <c r="U10" s="115">
+        <f t="shared" ref="U10:U11" si="30">T10/0.8*0.2</f>
+        <v>105709.93330560002</v>
+      </c>
+      <c r="V10" s="159"/>
+      <c r="W10" s="51"/>
+      <c r="X10" s="119"/>
+      <c r="Y10" s="119"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="68" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="103">
-        <f>((1575/12)*3)*0.6</f>
-        <v>236.25</v>
-      </c>
-      <c r="E11" s="104">
-        <v>0</v>
-      </c>
-      <c r="F11" s="104">
-        <f>(1575/12)*3</f>
+      <c r="D11" s="108">
+        <f>1575*5/12*0.6</f>
         <v>393.75</v>
       </c>
-      <c r="G11" s="89">
-        <v>393.75</v>
-      </c>
-      <c r="H11" s="89">
-        <v>393.75</v>
-      </c>
-      <c r="I11" s="89">
-        <v>0</v>
-      </c>
-      <c r="J11" s="89">
-        <v>0</v>
-      </c>
-      <c r="K11" s="104">
-        <f>(1575/12)*3*2</f>
-        <v>787.5</v>
-      </c>
-      <c r="L11" s="104">
-        <v>0</v>
-      </c>
-      <c r="M11" s="103">
-        <f>SUM(D11:L11)</f>
-        <v>2205</v>
-      </c>
-      <c r="N11" s="106">
-        <v>29555</v>
+      <c r="E11" s="109">
+        <v>0</v>
+      </c>
+      <c r="F11" s="109">
+        <f>1575*5/12</f>
+        <v>656.25</v>
+      </c>
+      <c r="G11" s="94">
+        <v>0</v>
+      </c>
+      <c r="H11" s="109">
+        <f>1575*5/12</f>
+        <v>656.25</v>
+      </c>
+      <c r="I11" s="94">
+        <v>0</v>
+      </c>
+      <c r="J11" s="94">
+        <v>0</v>
+      </c>
+      <c r="K11" s="109">
+        <f>1575*5/12*2</f>
+        <v>1312.5</v>
+      </c>
+      <c r="L11" s="109">
+        <v>0</v>
+      </c>
+      <c r="M11" s="109">
+        <v>0</v>
+      </c>
+      <c r="N11" s="109">
+        <v>0</v>
       </c>
       <c r="O11" s="109">
-        <v>29555</v>
-      </c>
-      <c r="Q11" s="110">
-        <f>((((D11*Rates!$G$25)+(UKRI!F11*Rates!$G$24)+((UKRI!H11+UKRI!L11)*Rates!$G$23)+(UKRI!K11*Rates!$G$16))*Rates!$I$11)*0.8)+N11+O11</f>
-        <v>156659.202709504</v>
-      </c>
-      <c r="R11" s="110">
-        <f>((((E11*Rates!$G$25)+(UKRI!H11*Rates!$G$24)+((UKRI!I11+UKRI!M11)*Rates!$G$23)+(UKRI!L11*Rates!$G$16))*Rates!$I$11)*0.2)</f>
-        <v>34755.555744000005</v>
-      </c>
-      <c r="S11" s="151"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="152" t="s">
-        <v>132</v>
-      </c>
-      <c r="V11" s="153"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="108">
+        <f t="shared" si="29"/>
+        <v>3018.75</v>
+      </c>
+      <c r="Q11" s="111">
+        <v>6000</v>
+      </c>
+      <c r="R11" s="114">
+        <v>20000</v>
+      </c>
+      <c r="T11" s="115">
+        <f>(((((D11*Rates!$G$25)+(UKRI!E11*Rates!$G$23)+(UKRI!F11*Rates!$G$24)+(UKRI!G11*Rates!$G$23)+(UKRI!H11*Rates!$I$22)+(UKRI!K11*Rates!$G$16)+(UKRI!L11*Rates!$G$23)+(UKRI!M10*Rates!$L$25)+(UKRI!N11*Rates!$G$23)+(UKRI!O11*Rates!$G$23))*Rates!$I$11)+Q11+R11)*0.8)</f>
+        <v>199097.58965984001</v>
+      </c>
+      <c r="U11" s="115">
+        <f t="shared" si="30"/>
+        <v>49774.397414960004</v>
+      </c>
+      <c r="V11" s="159"/>
+      <c r="W11" s="51"/>
+      <c r="X11" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y11" s="104"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="B12" s="154"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="89"/>
-      <c r="I12" s="89"/>
-      <c r="J12" s="89"/>
-      <c r="K12" s="89"/>
-      <c r="L12" s="89"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="109"/>
-      <c r="Q12" s="110"/>
-      <c r="R12" s="110"/>
-      <c r="S12" s="151"/>
-      <c r="T12" s="122"/>
-      <c r="U12" s="155"/>
-      <c r="V12" s="156"/>
+      <c r="B12" s="160"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="94"/>
+      <c r="M12" s="94"/>
+      <c r="N12" s="94"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="108"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="114"/>
+      <c r="T12" s="115"/>
+      <c r="U12" s="115"/>
+      <c r="V12" s="159"/>
+      <c r="W12" s="125"/>
+      <c r="X12" s="161"/>
+      <c r="Y12" s="162"/>
     </row>
     <row r="13" ht="21.75">
-      <c r="B13" s="125" t="s">
-        <v>133</v>
+      <c r="B13" s="127" t="s">
+        <v>142</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="126">
+      <c r="D13" s="128">
         <f>SUM(D7:D12)</f>
-        <v>4091.25</v>
-      </c>
-      <c r="E13" s="127">
-        <f t="shared" ref="E13:L13" si="26">SUM(E7:E12)</f>
-        <v>1476</v>
-      </c>
-      <c r="F13" s="127">
-        <f t="shared" si="26"/>
-        <v>3543.75</v>
-      </c>
-      <c r="G13" s="127">
+        <v>4248.75</v>
+      </c>
+      <c r="E13" s="129">
+        <f t="shared" ref="E13:K13" si="31">SUM(E7:E12)</f>
+        <v>2263.5</v>
+      </c>
+      <c r="F13" s="129">
+        <f t="shared" si="31"/>
+        <v>3018.75</v>
+      </c>
+      <c r="G13" s="129">
         <f>SUM(G7:G12)</f>
-        <v>3851.25</v>
-      </c>
-      <c r="H13" s="127">
-        <f t="shared" si="26"/>
-        <v>3851.25</v>
-      </c>
-      <c r="I13" s="127">
-        <f t="shared" si="26"/>
+        <v>1331.25</v>
+      </c>
+      <c r="H13" s="129">
+        <f t="shared" si="31"/>
+        <v>3562.5</v>
+      </c>
+      <c r="I13" s="129">
+        <f t="shared" si="31"/>
         <v>7</v>
       </c>
-      <c r="J13" s="127">
-        <f t="shared" si="26"/>
+      <c r="J13" s="129">
+        <f t="shared" si="31"/>
         <v>821</v>
       </c>
-      <c r="K13" s="127">
-        <f t="shared" si="26"/>
-        <v>5511.5</v>
-      </c>
-      <c r="L13" s="127">
-        <f t="shared" si="26"/>
-        <v>2047.5</v>
-      </c>
-      <c r="M13" s="126">
-        <f>SUM(M9:M12)</f>
-        <v>17796.5</v>
+      <c r="K13" s="129">
+        <f t="shared" si="31"/>
+        <v>6036.5</v>
+      </c>
+      <c r="L13" s="129">
+        <f>SUM(L7:L12)</f>
+        <v>945</v>
+      </c>
+      <c r="M13" s="129">
+        <f>SUM(M7:M12)</f>
+        <v>3150</v>
       </c>
       <c r="N13" s="129">
         <f>SUM(N7:N12)</f>
-        <v>100229</v>
-      </c>
-      <c r="O13" s="131">
+        <v>472.5</v>
+      </c>
+      <c r="O13" s="129">
         <f>SUM(O7:O12)</f>
-        <v>117509</v>
-      </c>
-      <c r="Q13" s="132">
-        <f>SUM(Q7:Q11)</f>
-        <v>965943.21957990387</v>
-      </c>
-      <c r="R13" s="132">
-        <f>SUM(R7:R11)</f>
-        <v>269678.46214399999</v>
-      </c>
-      <c r="S13" s="157">
-        <f>SUM(S7:S12)</f>
+        <v>420</v>
+      </c>
+      <c r="P13" s="128">
+        <f>SUM(P9:P12)</f>
+        <v>19975.25</v>
+      </c>
+      <c r="Q13" s="131">
+        <f>SUM(Q7:Q12)</f>
+        <v>23690</v>
+      </c>
+      <c r="R13" s="133">
+        <f>SUM(R7:R12)</f>
+        <v>82970</v>
+      </c>
+      <c r="T13" s="134">
+        <f>SUM(T7:T11)</f>
+        <v>1020749.37464224</v>
+      </c>
+      <c r="U13" s="134">
+        <f>SUM(U7:U11)</f>
+        <v>255187.34366056</v>
+      </c>
+      <c r="V13" s="163">
+        <f>SUM(V7:V12)</f>
         <v>371784.79000000004</v>
       </c>
-      <c r="T13" s="122"/>
-      <c r="U13" s="112">
-        <f>(Q13-S9)+S13</f>
-        <v>1294414.0095799039</v>
-      </c>
-      <c r="V13" s="113"/>
+      <c r="W13" s="125"/>
+      <c r="X13" s="117">
+        <f>(T13-V9)+V13</f>
+        <v>1349220.1646422399</v>
+      </c>
+      <c r="Y13" s="118"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="T14" s="122"/>
+      <c r="U14" s="142"/>
+      <c r="V14" s="41"/>
+      <c r="W14" s="125"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="Q15" s="138"/>
-      <c r="R15" s="138"/>
-      <c r="T15" s="122"/>
-      <c r="U15" s="152" t="s">
-        <v>148</v>
-      </c>
-      <c r="V15" s="153"/>
+      <c r="M15" s="139"/>
+      <c r="T15" s="138"/>
+      <c r="U15" s="138"/>
+      <c r="W15" s="125"/>
+      <c r="X15" s="103" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y15" s="104"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="Q16" s="158"/>
-      <c r="T16" s="122"/>
-      <c r="U16" s="155"/>
-      <c r="V16" s="156"/>
+      <c r="M16" s="139"/>
+      <c r="T16" s="142"/>
+      <c r="U16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="W16" s="125"/>
+      <c r="X16" s="161"/>
+      <c r="Y16" s="162"/>
     </row>
     <row r="17" ht="25.5" customHeight="1">
-      <c r="Q17" s="138"/>
-      <c r="R17" s="138"/>
-      <c r="T17" s="122"/>
-      <c r="U17" s="112">
-        <f>U9-U13</f>
-        <v>310983.99042009609</v>
-      </c>
-      <c r="V17" s="113"/>
+      <c r="D17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="M17" s="139"/>
+      <c r="T17" s="139" t="s">
+        <v>145</v>
+      </c>
+      <c r="U17" s="139" t="s">
+        <v>168</v>
+      </c>
+      <c r="V17" s="41"/>
+      <c r="W17" s="125"/>
+      <c r="X17" s="117">
+        <f>X9-X13</f>
+        <v>256177.83535776008</v>
+      </c>
+      <c r="Y17" s="118"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="N18" s="159"/>
-      <c r="O18" s="159"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
-      <c r="T18" s="122"/>
-      <c r="U18" s="160"/>
-      <c r="V18" s="160"/>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>169</v>
+      </c>
+      <c r="M18" s="139"/>
+      <c r="T18" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18" s="139" t="s">
+        <v>170</v>
+      </c>
+      <c r="W18" s="125"/>
+      <c r="X18" s="165"/>
+      <c r="Y18" s="165"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="N19" s="159"/>
-      <c r="O19" s="159"/>
-      <c r="P19" s="161"/>
-      <c r="Q19"/>
-      <c r="R19"/>
-      <c r="T19" s="122"/>
-      <c r="U19" s="137"/>
-      <c r="V19" s="137"/>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>171</v>
+      </c>
+      <c r="M19" s="139"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="140" t="s">
+        <v>35</v>
+      </c>
+      <c r="U19" s="139" t="s">
+        <v>172</v>
+      </c>
+      <c r="V19" s="148"/>
+      <c r="W19" s="125"/>
+      <c r="X19" s="137"/>
+      <c r="Y19" s="137"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="N20" s="159"/>
-      <c r="O20" s="159"/>
-      <c r="P20" s="161"/>
-      <c r="Q20" s="138"/>
-      <c r="R20" s="138"/>
-      <c r="T20" s="122"/>
-      <c r="U20" s="137"/>
-      <c r="V20" s="137"/>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>173</v>
+      </c>
+      <c r="M20" s="139"/>
+      <c r="S20" s="145"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20" s="148"/>
+      <c r="W20" s="125"/>
+      <c r="X20" s="137"/>
+      <c r="Y20" s="137"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="Q21" s="162"/>
-      <c r="R21" s="162"/>
-      <c r="S21" s="163"/>
-      <c r="T21" s="163"/>
-      <c r="U21" s="163"/>
-      <c r="V21" s="163"/>
-      <c r="W21" s="163"/>
-      <c r="X21" s="163"/>
-      <c r="Y21" s="163"/>
-      <c r="Z21" s="163"/>
-      <c r="AA21" s="163"/>
+      <c r="M21" s="139"/>
+      <c r="R21" s="140"/>
+      <c r="T21" s="142"/>
+      <c r="U21" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="W21" s="148"/>
+      <c r="X21" s="140"/>
+      <c r="Y21" s="148"/>
+      <c r="Z21" s="148"/>
+      <c r="AA21" s="148"/>
+      <c r="AB21" s="148"/>
+      <c r="AC21" s="148"/>
+      <c r="AD21" s="148"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="Q22" s="163"/>
-      <c r="R22" s="163"/>
-      <c r="S22" s="163"/>
-      <c r="T22" s="163"/>
-      <c r="U22" s="163"/>
-      <c r="V22" s="163"/>
-      <c r="W22" s="163"/>
-      <c r="X22" s="163"/>
-      <c r="Y22" s="163"/>
-      <c r="Z22" s="163"/>
-      <c r="AA22" s="163"/>
+      <c r="D22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="M22" s="139"/>
+      <c r="Q22" s="140"/>
+      <c r="R22" s="140"/>
+      <c r="T22" t="s">
+        <v>22</v>
+      </c>
+      <c r="U22" t="s">
+        <v>175</v>
+      </c>
+      <c r="W22" s="148"/>
+      <c r="X22" s="140"/>
+      <c r="Y22" s="148"/>
+      <c r="Z22" s="148"/>
+      <c r="AA22" s="148"/>
+      <c r="AB22" s="148"/>
+      <c r="AC22" s="148"/>
+      <c r="AD22" s="148"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="T23" s="122"/>
-      <c r="V23" s="164"/>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>176</v>
+      </c>
+      <c r="M23" s="139"/>
+      <c r="Q23" s="140"/>
+      <c r="R23" s="140"/>
+      <c r="T23" t="s">
+        <v>31</v>
+      </c>
+      <c r="U23" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="W23" s="125"/>
+      <c r="Y23" s="166"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="T24" s="122"/>
-      <c r="U24" s="137"/>
-      <c r="V24" s="137"/>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>178</v>
+      </c>
+      <c r="M24" s="139"/>
+      <c r="T24" t="s">
+        <v>34</v>
+      </c>
+      <c r="U24" s="140" t="s">
+        <v>179</v>
+      </c>
+      <c r="W24" s="125"/>
+      <c r="X24" s="137"/>
+      <c r="Y24" s="137"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="U25" s="137"/>
-      <c r="V25" s="137"/>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>180</v>
+      </c>
+      <c r="T25" t="s">
+        <v>37</v>
+      </c>
+      <c r="U25" s="140" t="s">
+        <v>181</v>
+      </c>
+      <c r="X25" s="137"/>
+      <c r="Y25" s="137"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="T26" s="122"/>
-      <c r="U26" s="165"/>
-      <c r="V26" s="165"/>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>182</v>
+      </c>
+      <c r="T26" t="s">
+        <v>38</v>
+      </c>
+      <c r="U26" s="140" t="s">
+        <v>183</v>
+      </c>
+      <c r="W26" s="125"/>
+      <c r="X26" s="167"/>
+      <c r="Y26" s="167"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="T28" t="s">
+        <v>30</v>
+      </c>
+      <c r="U28" t="s">
+        <v>185</v>
+      </c>
+      <c r="V28" s="41" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="T29" t="s">
+        <v>187</v>
+      </c>
+      <c r="U29" t="s">
+        <v>188</v>
+      </c>
+      <c r="V29" s="41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="T30" t="s">
+        <v>190</v>
+      </c>
+      <c r="U30" t="s">
+        <v>191</v>
+      </c>
+      <c r="V30" s="41" t="s">
+        <v>192</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B1:W2"/>
+    <mergeCell ref="B1:Z2"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:L4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="U4:V5"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="X26:Y26"/>
   </mergeCells>
-  <conditionalFormatting sqref="U12">
+  <conditionalFormatting sqref="X12">
     <cfRule type="iconSet" priority="2">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
@@ -7264,7 +7730,7 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U25">
+  <conditionalFormatting sqref="X25">
     <cfRule type="iconSet" priority="10">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
@@ -7273,7 +7739,7 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U16">
+  <conditionalFormatting sqref="X16">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
@@ -7291,7 +7757,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="12" operator="greaterThan" id="{0407AFA5-8F98-4AFD-8FCB-A21BE364183C}">
+          <x14:cfRule type="cellIs" priority="12" operator="greaterThan" id="{70C9C40C-C390-4E38-8D23-1C0F9E165274}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -7305,10 +7771,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>S7:S12</xm:sqref>
+          <xm:sqref>V7:V12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="13" operator="lessThan" id="{67E6CCCF-6A9E-4E6A-919B-D366F646F5F1}">
+          <x14:cfRule type="cellIs" priority="13" operator="lessThan" id="{66D6A3F3-F9A7-4EEB-BC8E-7A7305E6B0CF}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <font>
@@ -7322,7 +7788,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>S7:S12</xm:sqref>
+          <xm:sqref>V7:V12</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7381,7 +7847,7 @@
                 <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns3:FTBD_x005F_x0023_" minOccurs="0"/>
+                <xsd:element ref="ns3:FTBD_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x0023_" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -7492,7 +7958,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="FTBD_x005F_x0023_" ma:index="20" nillable="true" ma:displayName="FTBD#" ma:format="Dropdown" ma:internalName="FTBD_x005F_x0023_">
+    <xsd:element name="FTBD_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x0023_" ma:index="20" nillable="true" ma:displayName="FTBD#" ma:format="Dropdown" ma:internalName="FTBD_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x005F_x0023_">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text">
           <xsd:maxLength value="255"/>
